--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Attendance\ESE 2-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9808447E-2373-491C-8E9C-31EE2CE34497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067D9FD6-8B81-4694-A910-357808A39C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="58">
   <si>
     <t>SL</t>
   </si>
@@ -901,7 +901,7 @@
       </c>
       <c r="D4" s="8">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>46</v>
@@ -909,7 +909,9 @@
       <c r="F4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -981,7 +983,7 @@
       </c>
       <c r="D6" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>47</v>
@@ -989,7 +991,9 @@
       <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="D9" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>47</v>
@@ -1109,7 +1113,9 @@
       <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1141,7 +1147,7 @@
       </c>
       <c r="D10" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>47</v>
@@ -1149,7 +1155,9 @@
       <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1221,7 +1229,7 @@
       </c>
       <c r="D12" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>46</v>
@@ -1229,7 +1237,9 @@
       <c r="F12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1421,7 +1431,7 @@
       </c>
       <c r="D17" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>47</v>
@@ -1429,7 +1439,9 @@
       <c r="F17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1501,7 +1513,7 @@
       </c>
       <c r="D19" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>47</v>
@@ -1509,7 +1521,9 @@
       <c r="F19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1981,7 +1995,7 @@
       </c>
       <c r="D31" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>47</v>
@@ -1989,7 +2003,9 @@
       <c r="F31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -2021,7 +2037,7 @@
       </c>
       <c r="D32" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>47</v>
@@ -2029,7 +2045,9 @@
       <c r="F32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -2301,7 +2319,7 @@
       </c>
       <c r="D39" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>46</v>
@@ -2309,7 +2327,9 @@
       <c r="F39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G39" s="1"/>
+      <c r="G39" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -2341,7 +2361,7 @@
       </c>
       <c r="D40" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>47</v>
@@ -2349,7 +2369,9 @@
       <c r="F40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G40" s="1"/>
+      <c r="G40" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -2381,7 +2403,7 @@
       </c>
       <c r="D41" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>46</v>
@@ -2389,7 +2411,9 @@
       <c r="F41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -2429,7 +2453,9 @@
       <c r="F42" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -2461,7 +2487,7 @@
       </c>
       <c r="D43" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>47</v>
@@ -2469,7 +2495,9 @@
       <c r="F43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="1"/>
+      <c r="G43" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -2501,7 +2529,7 @@
       </c>
       <c r="D44" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>47</v>
@@ -2509,7 +2537,9 @@
       <c r="F44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="1"/>
+      <c r="G44" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>

--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067D9FD6-8B81-4694-A910-357808A39C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9AFE3A-56FC-4C95-B223-FDC0F92918A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="59">
   <si>
     <t>SL</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>p</t>
   </si>
 </sst>
 </file>
@@ -951,7 +954,9 @@
       <c r="F5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -991,7 +996,7 @@
       <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H6" s="1"/>
@@ -1033,7 +1038,9 @@
       <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1073,7 +1080,9 @@
       <c r="F8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1113,7 +1122,7 @@
       <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H9" s="1"/>
@@ -1155,7 +1164,7 @@
       <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H10" s="1"/>
@@ -1197,7 +1206,9 @@
       <c r="F11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -1279,7 +1290,9 @@
       <c r="F13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1311,7 +1324,7 @@
       </c>
       <c r="D14" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>46</v>
@@ -1319,7 +1332,9 @@
       <c r="F14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1359,7 +1374,9 @@
       <c r="F15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1399,7 +1416,9 @@
       <c r="F16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1439,7 +1458,7 @@
       <c r="F17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H17" s="1"/>
@@ -1481,7 +1500,9 @@
       <c r="F18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1521,7 +1542,7 @@
       <c r="F19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H19" s="1"/>
@@ -1563,7 +1584,9 @@
       <c r="F20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1603,7 +1626,9 @@
       <c r="F21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1643,7 +1668,9 @@
       <c r="F22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1675,7 +1702,7 @@
       </c>
       <c r="D23" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>47</v>
@@ -1683,7 +1710,9 @@
       <c r="F23" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1715,7 +1744,7 @@
       </c>
       <c r="D24" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>47</v>
@@ -1723,7 +1752,9 @@
       <c r="F24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1755,7 +1786,7 @@
       </c>
       <c r="D25" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>46</v>
@@ -1763,7 +1794,9 @@
       <c r="F25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1803,7 +1836,9 @@
       <c r="F26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1843,7 +1878,9 @@
       <c r="F27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1883,7 +1920,9 @@
       <c r="F28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1923,7 +1962,9 @@
       <c r="F29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1963,7 +2004,9 @@
       <c r="F30" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="1"/>
+      <c r="G30" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -2003,7 +2046,7 @@
       <c r="F31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H31" s="1"/>
@@ -2045,7 +2088,7 @@
       <c r="F32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H32" s="1"/>
@@ -2087,7 +2130,9 @@
       <c r="F33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -2127,7 +2172,9 @@
       <c r="F34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -2159,7 +2206,7 @@
       </c>
       <c r="D35" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>47</v>
@@ -2167,7 +2214,9 @@
       <c r="F35" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -2207,7 +2256,9 @@
       <c r="F36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="1"/>
+      <c r="G36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -2247,7 +2298,9 @@
       <c r="F37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -2287,7 +2340,9 @@
       <c r="F38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G38" s="1"/>
+      <c r="G38" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -2327,7 +2382,7 @@
       <c r="F39" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H39" s="1"/>
@@ -2369,7 +2424,7 @@
       <c r="F40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H40" s="1"/>
@@ -2411,7 +2466,7 @@
       <c r="F41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H41" s="1"/>
@@ -2453,7 +2508,7 @@
       <c r="F42" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H42" s="1"/>
@@ -2495,7 +2550,7 @@
       <c r="F43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H43" s="1"/>
@@ -2537,7 +2592,7 @@
       <c r="F44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H44" s="1"/>

--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9AFE3A-56FC-4C95-B223-FDC0F92918A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E191A85-41EE-40F1-8746-E9F0961C9954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="59">
   <si>
     <t>SL</t>
   </si>
@@ -725,8 +725,8 @@
     <col min="3" max="3" width="48.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="27.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="24" width="30.77734375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="24" width="30.77734375" style="2" customWidth="1"/>
     <col min="25" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -874,7 +874,9 @@
       <c r="G3" s="9">
         <v>46267</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="9">
+        <v>46274</v>
+      </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -946,7 +948,7 @@
       </c>
       <c r="D5" s="8">
         <f t="shared" ref="D5:D44" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>47</v>
@@ -957,7 +959,9 @@
       <c r="G5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="D39" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>46</v>
@@ -2385,7 +2389,9 @@
       <c r="G39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="1"/>
+      <c r="H39" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2458,7 +2464,7 @@
       </c>
       <c r="D41" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>46</v>
@@ -2469,7 +2475,9 @@
       <c r="G41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="1"/>
+      <c r="H41" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>

--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E191A85-41EE-40F1-8746-E9F0961C9954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1294A73-B587-468A-8F59-1C84CCFB2F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
   <si>
     <t>SL</t>
   </si>
@@ -203,27 +203,40 @@
     <t>Assignment 3</t>
   </si>
   <si>
-    <t>Assignmnet 4</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
     <t>Knitting Action</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>p</t>
+  </si>
+  <si>
+    <t>Comments on 1st Assignemnt</t>
+  </si>
+  <si>
+    <t>COPY</t>
+  </si>
+  <si>
+    <t>Comments on 2nd Assignemnt</t>
+  </si>
+  <si>
+    <t>Comments on 3rd Assignemnt</t>
+  </si>
+  <si>
+    <t>Warp Knitting Lapping</t>
+  </si>
+  <si>
+    <t>Held, Tuck Loop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -273,7 +286,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,6 +346,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -362,7 +381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -400,13 +419,19 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -415,12 +440,45 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -731,10 +789,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="18"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -906,7 +964,7 @@
       </c>
       <c r="D4" s="8">
         <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>46</v>
@@ -917,7 +975,9 @@
       <c r="G4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -959,7 +1019,7 @@
       <c r="G5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
@@ -992,7 +1052,7 @@
       </c>
       <c r="D6" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>47</v>
@@ -1003,7 +1063,9 @@
       <c r="G6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1045,7 +1107,9 @@
       <c r="G7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1087,7 +1151,9 @@
       <c r="G8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1118,7 +1184,7 @@
       </c>
       <c r="D9" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>47</v>
@@ -1129,7 +1195,9 @@
       <c r="G9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1160,7 +1228,7 @@
       </c>
       <c r="D10" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>47</v>
@@ -1171,7 +1239,9 @@
       <c r="G10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1213,7 +1283,9 @@
       <c r="G11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1244,7 +1316,7 @@
       </c>
       <c r="D12" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>46</v>
@@ -1255,7 +1327,9 @@
       <c r="G12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1297,7 +1371,9 @@
       <c r="G13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1328,7 +1404,7 @@
       </c>
       <c r="D14" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>46</v>
@@ -1339,7 +1415,9 @@
       <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1381,7 +1459,9 @@
       <c r="G15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1423,7 +1503,9 @@
       <c r="G16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1454,7 +1536,7 @@
       </c>
       <c r="D17" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>47</v>
@@ -1465,7 +1547,9 @@
       <c r="G17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1505,9 +1589,11 @@
         <v>47</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1538,7 +1624,7 @@
       </c>
       <c r="D19" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>47</v>
@@ -1549,7 +1635,9 @@
       <c r="G19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1589,9 +1677,11 @@
         <v>47</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1631,9 +1721,11 @@
         <v>47</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1673,9 +1765,11 @@
         <v>47</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H22" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1706,7 +1800,7 @@
       </c>
       <c r="D23" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>47</v>
@@ -1715,9 +1809,11 @@
         <v>46</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1748,7 +1844,7 @@
       </c>
       <c r="D24" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>47</v>
@@ -1757,9 +1853,11 @@
         <v>46</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1790,7 +1888,7 @@
       </c>
       <c r="D25" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>46</v>
@@ -1799,9 +1897,11 @@
         <v>47</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H25" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1841,9 +1941,11 @@
         <v>47</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H26" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1883,9 +1985,11 @@
         <v>47</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1925,9 +2029,11 @@
         <v>47</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H28" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1967,9 +2073,11 @@
         <v>47</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H29" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2009,9 +2117,11 @@
         <v>47</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2042,7 +2152,7 @@
       </c>
       <c r="D31" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>47</v>
@@ -2053,7 +2163,9 @@
       <c r="G31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="1"/>
+      <c r="H31" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2084,7 +2196,7 @@
       </c>
       <c r="D32" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>47</v>
@@ -2095,7 +2207,9 @@
       <c r="G32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="H32" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2137,7 +2251,9 @@
       <c r="G33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2179,7 +2295,9 @@
       <c r="G34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="1"/>
+      <c r="H34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2210,7 +2328,7 @@
       </c>
       <c r="D35" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>47</v>
@@ -2221,7 +2339,9 @@
       <c r="G35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H35" s="1"/>
+      <c r="H35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2263,7 +2383,9 @@
       <c r="G36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2305,7 +2427,9 @@
       <c r="G37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="H37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2347,7 +2471,9 @@
       <c r="G38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H38" s="1"/>
+      <c r="H38" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2389,7 +2515,7 @@
       <c r="G39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I39" s="1"/>
@@ -2422,7 +2548,7 @@
       </c>
       <c r="D40" s="8">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>47</v>
@@ -2433,7 +2559,9 @@
       <c r="G40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H40" s="1"/>
+      <c r="H40" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2475,7 +2603,7 @@
       <c r="G41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I41" s="1"/>
@@ -2508,7 +2636,7 @@
       </c>
       <c r="D42" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>46</v>
@@ -2519,7 +2647,9 @@
       <c r="G42" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="1"/>
+      <c r="H42" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2550,7 +2680,7 @@
       </c>
       <c r="D43" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>47</v>
@@ -2561,7 +2691,9 @@
       <c r="G43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="1"/>
+      <c r="H43" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2592,7 +2724,7 @@
       </c>
       <c r="D44" s="8">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>47</v>
@@ -2603,7 +2735,9 @@
       <c r="G44" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H44" s="1"/>
+      <c r="H44" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2626,11 +2760,15 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D44">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
-      <formula>0.8</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+      <formula>0.6</formula>
+      <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2640,24 +2778,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A46F8F3-1BFE-4AF0-A2BB-D8B7450A48F3}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="49.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="15.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="4" max="4" width="22.109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11" style="2" customWidth="1"/>
+    <col min="9" max="11" width="27.77734375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="18"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -2670,15 +2810,21 @@
       <c r="F1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="17"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H1" s="19"/>
+      <c r="I1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -2690,15 +2836,21 @@
         <v>49</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2708,26 +2860,27 @@
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="14">
-        <v>20</v>
-      </c>
-      <c r="I3" s="14">
+      <c r="D3" s="15">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E3" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="F3" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="G3" s="13">
+        <f t="shared" ref="G3:G44" si="0">SUM(D3:F3)</f>
+        <v>22.5</v>
+      </c>
+      <c r="H3" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -2737,20 +2890,24 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15">
-        <f>SUM(D4:G4)</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="15">
-        <f>(H4/20)*7.5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D4" s="14">
+        <v>5</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H4" s="17">
+        <f>G4/3</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <f>A4+1</f>
         <v>2</v>
@@ -2761,20 +2918,24 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15">
-        <f t="shared" ref="H5:H31" si="0">SUM(D5:G5)</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="15">
-        <f t="shared" ref="I5:I44" si="1">(H5/20)*7.5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D5" s="14">
+        <v>7</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H5" s="17">
+        <f t="shared" ref="H5:H44" si="1">G5/3</f>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A44" si="2">A5+1</f>
         <v>3</v>
@@ -2785,20 +2946,24 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D6" s="14">
+        <v>6</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H6" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -2809,20 +2974,26 @@
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D7" s="14">
+        <v>3</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H7" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -2833,20 +3004,24 @@
       <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D8" s="14">
+        <v>7</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H8" s="17">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -2857,20 +3032,24 @@
       <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D9" s="14">
+        <v>7</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H9" s="17">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -2881,20 +3060,24 @@
       <c r="C10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D10" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H10" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -2905,20 +3088,24 @@
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D11" s="14">
+        <v>7</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H11" s="17">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -2929,20 +3116,24 @@
       <c r="C12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D12" s="14">
+        <v>6</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -2953,20 +3144,24 @@
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D13" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -2977,20 +3172,24 @@
       <c r="C14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D14" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H14" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -3001,20 +3200,26 @@
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -3025,20 +3230,24 @@
       <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D16" s="14">
+        <v>7</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H16" s="17">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -3049,20 +3258,24 @@
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D17" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -3073,20 +3286,24 @@
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D18" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="H18" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -3097,20 +3314,24 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D19" s="14">
+        <v>6</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H19" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -3121,20 +3342,24 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D20" s="14">
+        <v>6</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H20" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3145,20 +3370,24 @@
       <c r="C21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D21" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H21" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -3169,20 +3398,24 @@
       <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D22" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H22" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -3193,20 +3426,26 @@
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H23" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -3217,20 +3456,24 @@
       <c r="C24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D24" s="14">
+        <v>7</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H24" s="17">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -3241,20 +3484,24 @@
       <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D25" s="14">
+        <v>4</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H25" s="17">
+        <f t="shared" si="1"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -3265,20 +3512,24 @@
       <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D26" s="14">
+        <v>5.5</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="H26" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -3289,20 +3540,24 @@
       <c r="C27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D27" s="14">
+        <v>7</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H27" s="17">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -3313,20 +3568,24 @@
       <c r="C28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D28" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="H28" s="17">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -3337,20 +3596,24 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D29" s="14">
+        <v>6.5</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H29" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -3361,20 +3624,24 @@
       <c r="C30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D30" s="14">
+        <v>6</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H30" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -3385,20 +3652,26 @@
       <c r="C31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D31" s="14">
+        <v>3</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H31" s="17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -3409,20 +3682,24 @@
       <c r="C32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1">
+        <v>4.5</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="15">
-        <f t="shared" ref="H32:H44" si="3">SUM(D32:G32)</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G32" s="14">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="H32" s="17">
+        <f t="shared" si="1"/>
+        <v>1.5</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -3433,20 +3710,24 @@
       <c r="C33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G33" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H33" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -3457,20 +3738,24 @@
       <c r="C34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1">
+        <v>6</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G34" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H34" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -3481,20 +3766,24 @@
       <c r="C35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="1"/>
+      <c r="D35" s="1">
+        <v>5</v>
+      </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G35" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="H35" s="17">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -3505,20 +3794,24 @@
       <c r="C36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="1"/>
+      <c r="D36" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G36" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H36" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -3529,20 +3822,24 @@
       <c r="C37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G37" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="H37" s="17">
+        <f t="shared" si="1"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -3553,20 +3850,24 @@
       <c r="C38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="1"/>
+      <c r="D38" s="1">
+        <v>6</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G38" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H38" s="17">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -3577,20 +3878,22 @@
       <c r="C39" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="1"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="15">
-        <f t="shared" si="3"/>
+      <c r="G39" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I39" s="15">
+      <c r="H39" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -3601,20 +3904,22 @@
       <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="1"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="15">
-        <f t="shared" si="3"/>
+      <c r="G40" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I40" s="15">
+      <c r="H40" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -3625,20 +3930,22 @@
       <c r="C41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="1"/>
+      <c r="D41" s="16"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="15">
-        <f t="shared" si="3"/>
+      <c r="G41" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I41" s="15">
+      <c r="H41" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -3649,20 +3956,24 @@
       <c r="C42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="1"/>
+      <c r="D42" s="1">
+        <v>5.5</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="15">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G42" s="14">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="H42" s="17">
+        <f t="shared" si="1"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -3673,20 +3984,22 @@
       <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="1"/>
+      <c r="D43" s="16"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="15">
-        <f t="shared" si="3"/>
+      <c r="G43" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I43" s="15">
+      <c r="H43" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -3697,28 +4010,30 @@
       <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="1"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="15">
-        <f t="shared" si="3"/>
+      <c r="G44" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I44" s="15">
+      <c r="H44" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H1:I2"/>
+    <mergeCell ref="G1:H2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="J1:J3"/>
+    <mergeCell ref="K1:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3:G3" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1294A73-B587-468A-8F59-1C84CCFB2F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E24F88A-1E57-438C-9F8E-D0E331393B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ESE 2-1 Attendance'!$E$3:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ESE 2-1 Attendance'!$F$3:$Y$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t>SL</t>
   </si>
@@ -228,6 +250,9 @@
   </si>
   <si>
     <t>Held, Tuck Loop</t>
+  </si>
+  <si>
+    <t>Marks</t>
   </si>
 </sst>
 </file>
@@ -381,7 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -443,12 +468,43 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -476,26 +532,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -775,20 +811,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X44"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y44"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="27.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="24" width="30.77734375" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="8.88671875" style="21"/>
+    <col min="6" max="7" width="27.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="25" width="30.77734375" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>45</v>
       </c>
@@ -797,7 +834,7 @@
         <v>43</v>
       </c>
       <c r="D1" s="4"/>
-      <c r="E1" s="5"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -817,8 +854,9 @@
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y1" s="5"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -830,87 +868,88 @@
         <v>49</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="6">
+      <c r="E2" s="4"/>
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="6">
-        <f>E2+1</f>
+      <c r="G2" s="6">
+        <f>F2+1</f>
         <v>2</v>
       </c>
-      <c r="G2" s="6">
-        <f t="shared" ref="G2:X2" si="0">F2+1</f>
+      <c r="H2" s="6">
+        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
         <v>3</v>
       </c>
-      <c r="H2" s="6">
+      <c r="I2" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I2" s="6">
+      <c r="J2" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J2" s="6">
+      <c r="K2" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K2" s="6">
+      <c r="L2" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L2" s="6">
+      <c r="M2" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M2" s="6">
+      <c r="N2" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="N2" s="6">
+      <c r="O2" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O2" s="6">
+      <c r="P2" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P2" s="6">
+      <c r="Q2" s="6">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="Q2" s="6">
-        <f>P2+1</f>
+      <c r="R2" s="6">
+        <f>Q2+1</f>
         <v>13</v>
       </c>
-      <c r="R2" s="6">
+      <c r="S2" s="6">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="S2" s="6">
+      <c r="T2" s="6">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="T2" s="6">
+      <c r="U2" s="6">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="U2" s="6">
+      <c r="V2" s="6">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="V2" s="6">
-        <f>U2+1</f>
+      <c r="W2" s="6">
+        <f>V2+1</f>
         <v>18</v>
       </c>
-      <c r="W2" s="6">
+      <c r="X2" s="6">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="X2" s="6">
+      <c r="Y2" s="6">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -923,20 +962,24 @@
       <c r="D3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="9">
         <v>46257</v>
       </c>
-      <c r="F3" s="9">
+      <c r="G3" s="9">
         <v>46264</v>
       </c>
-      <c r="G3" s="9">
+      <c r="H3" s="9">
         <v>46267</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>46274</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+      <c r="J3" s="9">
+        <v>46278</v>
+      </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
@@ -951,8 +994,9 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y3" s="9"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -963,22 +1007,25 @@
         <v>3</v>
       </c>
       <c r="D4" s="8">
-        <f>COUNTIF(E4:X4,"P")/(COUNTIF(E4:X4,"P")+COUNTIF(E4:X4,"A"))</f>
+        <f>COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="1" cm="1">
+        <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G4" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -994,8 +1041,9 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y4" s="1"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <f>A4+1</f>
         <v>2</v>
@@ -1007,11 +1055,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" ref="D5:D44" si="1">COUNTIF(E5:X5,"P")/(COUNTIF(E5:X5,"P")+COUNTIF(E5:X5,"A"))</f>
+        <f>COUNTIF(F5:Y5,"P")/(COUNTIF(F5:Y5,"P")+COUNTIF(F5:Y5,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>47</v>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>47</v>
@@ -1019,10 +1068,12 @@
       <c r="G5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1038,10 +1089,11 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y5" s="1"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A44" si="2">A5+1</f>
+        <f t="shared" ref="A6:A44" si="1">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -1051,22 +1103,25 @@
         <v>5</v>
       </c>
       <c r="D6" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F6:Y6,"P")/(COUNTIF(F6:Y6,"P")+COUNTIF(F6:Y6,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>47</v>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1082,10 +1137,11 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y6" s="1"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -1095,11 +1151,12 @@
         <v>6</v>
       </c>
       <c r="D7" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F7:Y7,"P")/(COUNTIF(F7:Y7,"P")+COUNTIF(F7:Y7,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.IFS(D7&gt;=90%,7.5,D7&gt;=80%,6,D7&gt;=70%,4.5,D7&gt;=60%,3,D7&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>47</v>
@@ -1110,7 +1167,9 @@
       <c r="H7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1126,10 +1185,11 @@
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -1139,11 +1199,12 @@
         <v>7</v>
       </c>
       <c r="D8" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F8:Y8,"P")/(COUNTIF(F8:Y8,"P")+COUNTIF(F8:Y8,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>47</v>
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.IFS(D8&gt;=90%,7.5,D8&gt;=80%,6,D8&gt;=70%,4.5,D8&gt;=60%,3,D8&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>47</v>
@@ -1154,7 +1215,9 @@
       <c r="H8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1170,10 +1233,11 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -1183,22 +1247,25 @@
         <v>8</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F9:Y9,"P")/(COUNTIF(F9:Y9,"P")+COUNTIF(F9:Y9,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>47</v>
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1214,10 +1281,11 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y9" s="1"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -1227,22 +1295,25 @@
         <v>9</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F10:Y10,"P")/(COUNTIF(F10:Y10,"P")+COUNTIF(F10:Y10,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>47</v>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1258,10 +1329,11 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y10" s="1"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -1271,11 +1343,12 @@
         <v>10</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F11:Y11,"P")/(COUNTIF(F11:Y11,"P")+COUNTIF(F11:Y11,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>47</v>
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>47</v>
@@ -1286,7 +1359,9 @@
       <c r="H11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1302,10 +1377,11 @@
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <f t="shared" si="2"/>
+      <c r="Y11" s="1"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -1315,22 +1391,25 @@
         <v>11</v>
       </c>
       <c r="D12" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F12:Y12,"P")/(COUNTIF(F12:Y12,"P")+COUNTIF(F12:Y12,"A"))</f>
         <v>0.5</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>46</v>
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>47</v>
+      <c r="G12" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1346,10 +1425,11 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y12" s="1"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -1359,11 +1439,12 @@
         <v>12</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F13:Y13,"P")/(COUNTIF(F13:Y13,"P")+COUNTIF(F13:Y13,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>47</v>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.IFS(D13&gt;=90%,7.5,D13&gt;=80%,6,D13&gt;=70%,4.5,D13&gt;=60%,3,D13&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>47</v>
@@ -1374,7 +1455,9 @@
       <c r="H13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1390,10 +1473,11 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y13" s="1"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -1403,22 +1487,25 @@
         <v>13</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F14:Y14,"P")/(COUNTIF(F14:Y14,"P")+COUNTIF(F14:Y14,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="1" cm="1">
+        <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1434,10 +1521,11 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y14" s="1"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -1447,11 +1535,12 @@
         <v>14</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F15:Y15,"P")/(COUNTIF(F15:Y15,"P")+COUNTIF(F15:Y15,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>47</v>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xlfn.IFS(D15&gt;=90%,7.5,D15&gt;=80%,6,D15&gt;=70%,4.5,D15&gt;=60%,3,D15&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>47</v>
@@ -1462,7 +1551,9 @@
       <c r="H15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1478,10 +1569,11 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y15" s="1"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -1491,11 +1583,12 @@
         <v>15</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F16:Y16,"P")/(COUNTIF(F16:Y16,"P")+COUNTIF(F16:Y16,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>47</v>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xlfn.IFS(D16&gt;=90%,7.5,D16&gt;=80%,6,D16&gt;=70%,4.5,D16&gt;=60%,3,D16&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>47</v>
@@ -1506,7 +1599,9 @@
       <c r="H16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="1"/>
+      <c r="I16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1522,10 +1617,11 @@
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y16" s="1"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -1535,22 +1631,25 @@
         <v>16</v>
       </c>
       <c r="D17" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F17:Y17,"P")/(COUNTIF(F17:Y17,"P")+COUNTIF(F17:Y17,"A"))</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>46</v>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="1"/>
+      <c r="H17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1566,10 +1665,11 @@
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y17" s="1"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -1579,22 +1679,25 @@
         <v>17</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F18:Y18,"P")/(COUNTIF(F18:Y18,"P")+COUNTIF(F18:Y18,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>47</v>
+      <c r="E18" s="1" cm="1">
+        <f t="array" ref="E18">_xlfn.IFS(D18&gt;=90%,7.5,D18&gt;=80%,6,D18&gt;=70%,4.5,D18&gt;=60%,3,D18&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1610,10 +1713,11 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y18" s="1"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -1623,22 +1727,25 @@
         <v>18</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F19:Y19,"P")/(COUNTIF(F19:Y19,"P")+COUNTIF(F19:Y19,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>47</v>
+      <c r="E19" s="1" cm="1">
+        <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1654,10 +1761,11 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -1667,22 +1775,25 @@
         <v>19</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F20:Y20,"P")/(COUNTIF(F20:Y20,"P")+COUNTIF(F20:Y20,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>47</v>
+      <c r="E20" s="1" cm="1">
+        <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1698,10 +1809,11 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y20" s="1"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -1711,22 +1823,25 @@
         <v>20</v>
       </c>
       <c r="D21" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F21:Y21,"P")/(COUNTIF(F21:Y21,"P")+COUNTIF(F21:Y21,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>47</v>
+      <c r="E21" s="1" cm="1">
+        <f t="array" ref="E21">_xlfn.IFS(D21&gt;=90%,7.5,D21&gt;=80%,6,D21&gt;=70%,4.5,D21&gt;=60%,3,D21&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1742,10 +1857,11 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y21" s="1"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -1755,22 +1871,25 @@
         <v>21</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F22:Y22,"P")/(COUNTIF(F22:Y22,"P")+COUNTIF(F22:Y22,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>47</v>
+      <c r="E22" s="1" cm="1">
+        <f t="array" ref="E22">_xlfn.IFS(D22&gt;=90%,7.5,D22&gt;=80%,6,D22&gt;=70%,4.5,D22&gt;=60%,3,D22&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1786,10 +1905,11 @@
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y22" s="1"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -1799,22 +1919,25 @@
         <v>22</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F23:Y23,"P")/(COUNTIF(F23:Y23,"P")+COUNTIF(F23:Y23,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="7" t="s">
+      <c r="E23" s="1" cm="1">
+        <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1830,10 +1953,11 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y23" s="1"/>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -1843,22 +1967,25 @@
         <v>23</v>
       </c>
       <c r="D24" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F24:Y24,"P")/(COUNTIF(F24:Y24,"P")+COUNTIF(F24:Y24,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="7" t="s">
+      <c r="E24" s="1" cm="1">
+        <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="1"/>
+      <c r="I24" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1874,10 +2001,11 @@
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y24" s="1"/>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -1887,22 +2015,25 @@
         <v>24</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F25:Y25,"P")/(COUNTIF(F25:Y25,"P")+COUNTIF(F25:Y25,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="1" cm="1">
+        <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="G25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1918,10 +2049,11 @@
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y25" s="1"/>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -1931,22 +2063,25 @@
         <v>25</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F26:Y26,"P")/(COUNTIF(F26:Y26,"P")+COUNTIF(F26:Y26,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>47</v>
+      <c r="E26" s="1" cm="1">
+        <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I26" s="1"/>
+      <c r="I26" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1962,10 +2097,11 @@
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y26" s="1"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -1975,22 +2111,25 @@
         <v>26</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F27:Y27,"P")/(COUNTIF(F27:Y27,"P")+COUNTIF(F27:Y27,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>47</v>
+      <c r="E27" s="1" cm="1">
+        <f t="array" ref="E27">_xlfn.IFS(D27&gt;=90%,7.5,D27&gt;=80%,6,D27&gt;=70%,4.5,D27&gt;=60%,3,D27&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -2006,10 +2145,11 @@
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y27" s="1"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -2019,22 +2159,25 @@
         <v>27</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F28:Y28,"P")/(COUNTIF(F28:Y28,"P")+COUNTIF(F28:Y28,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>47</v>
+      <c r="E28" s="1" cm="1">
+        <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -2050,10 +2193,11 @@
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y28" s="1"/>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -2063,22 +2207,25 @@
         <v>28</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F29:Y29,"P")/(COUNTIF(F29:Y29,"P")+COUNTIF(F29:Y29,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>47</v>
+      <c r="E29" s="1" cm="1">
+        <f t="array" ref="E29">_xlfn.IFS(D29&gt;=90%,7.5,D29&gt;=80%,6,D29&gt;=70%,4.5,D29&gt;=60%,3,D29&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I29" s="1"/>
+      <c r="I29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -2094,10 +2241,11 @@
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y29" s="1"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -2107,22 +2255,25 @@
         <v>29</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F30:Y30,"P")/(COUNTIF(F30:Y30,"P")+COUNTIF(F30:Y30,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>47</v>
+      <c r="E30" s="1" cm="1">
+        <f t="array" ref="E30">_xlfn.IFS(D30&gt;=90%,7.5,D30&gt;=80%,6,D30&gt;=70%,4.5,D30&gt;=60%,3,D30&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -2138,10 +2289,11 @@
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <f t="shared" si="2"/>
+      <c r="Y30" s="1"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -2151,22 +2303,25 @@
         <v>30</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F31:Y31,"P")/(COUNTIF(F31:Y31,"P")+COUNTIF(F31:Y31,"A"))</f>
         <v>0.5</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>46</v>
+      <c r="E31" s="1" cm="1">
+        <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I31" s="1"/>
+      <c r="H31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2182,10 +2337,11 @@
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y31" s="1"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -2195,22 +2351,25 @@
         <v>31</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F32:Y32,"P")/(COUNTIF(F32:Y32,"P")+COUNTIF(F32:Y32,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>47</v>
+      <c r="E32" s="1" cm="1">
+        <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="1"/>
+      <c r="I32" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2226,10 +2385,11 @@
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y32" s="1"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B33" s="1">
@@ -2239,11 +2399,12 @@
         <v>32</v>
       </c>
       <c r="D33" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F33:Y33,"P")/(COUNTIF(F33:Y33,"P")+COUNTIF(F33:Y33,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>47</v>
+      <c r="E33" s="1" cm="1">
+        <f t="array" ref="E33">_xlfn.IFS(D33&gt;=90%,7.5,D33&gt;=80%,6,D33&gt;=70%,4.5,D33&gt;=60%,3,D33&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>47</v>
@@ -2254,7 +2415,9 @@
       <c r="H33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2270,10 +2433,11 @@
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y33" s="1"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B34" s="1">
@@ -2283,11 +2447,12 @@
         <v>33</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F34:Y34,"P")/(COUNTIF(F34:Y34,"P")+COUNTIF(F34:Y34,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>47</v>
+      <c r="E34" s="1" cm="1">
+        <f t="array" ref="E34">_xlfn.IFS(D34&gt;=90%,7.5,D34&gt;=80%,6,D34&gt;=70%,4.5,D34&gt;=60%,3,D34&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>47</v>
@@ -2298,7 +2463,9 @@
       <c r="H34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I34" s="1"/>
+      <c r="I34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2314,10 +2481,11 @@
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y34" s="1"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B35" s="1">
@@ -2327,22 +2495,25 @@
         <v>34</v>
       </c>
       <c r="D35" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F35:Y35,"P")/(COUNTIF(F35:Y35,"P")+COUNTIF(F35:Y35,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="7" t="s">
+      <c r="E35" s="1" cm="1">
+        <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="H35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -2358,10 +2529,11 @@
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y35" s="1"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="B36" s="11">
@@ -2371,11 +2543,12 @@
         <v>35</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F36:Y36,"P")/(COUNTIF(F36:Y36,"P")+COUNTIF(F36:Y36,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>47</v>
+      <c r="E36" s="1" cm="1">
+        <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>47</v>
@@ -2386,7 +2559,9 @@
       <c r="H36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2402,10 +2577,11 @@
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y36" s="1"/>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B37" s="1">
@@ -2415,11 +2591,12 @@
         <v>36</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F37:Y37,"P")/(COUNTIF(F37:Y37,"P")+COUNTIF(F37:Y37,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>47</v>
+      <c r="E37" s="1" cm="1">
+        <f t="array" ref="E37">_xlfn.IFS(D37&gt;=90%,7.5,D37&gt;=80%,6,D37&gt;=70%,4.5,D37&gt;=60%,3,D37&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>47</v>
@@ -2430,7 +2607,9 @@
       <c r="H37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -2446,10 +2625,11 @@
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y37" s="1"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="B38" s="1">
@@ -2459,11 +2639,12 @@
         <v>37</v>
       </c>
       <c r="D38" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F38:Y38,"P")/(COUNTIF(F38:Y38,"P")+COUNTIF(F38:Y38,"A"))</f>
         <v>1</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>47</v>
+      <c r="E38" s="1" cm="1">
+        <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
+        <v>7.5</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>47</v>
@@ -2474,7 +2655,9 @@
       <c r="H38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2490,10 +2673,11 @@
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y38" s="1"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B39" s="1">
@@ -2503,22 +2687,25 @@
         <v>50</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F39:Y39,"P")/(COUNTIF(F39:Y39,"P")+COUNTIF(F39:Y39,"A"))</f>
         <v>0.25</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="1" cm="1">
+        <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>46</v>
+      <c r="G39" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I39" s="1"/>
+      <c r="I39" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2534,10 +2721,11 @@
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y39" s="1"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B40" s="1">
@@ -2547,22 +2735,25 @@
         <v>38</v>
       </c>
       <c r="D40" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F40:Y40,"P")/(COUNTIF(F40:Y40,"P")+COUNTIF(F40:Y40,"A"))</f>
         <v>0.5</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>46</v>
+      <c r="E40" s="1" cm="1">
+        <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I40" s="1"/>
+      <c r="H40" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2578,10 +2769,11 @@
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y40" s="1"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B41" s="1">
@@ -2591,22 +2783,25 @@
         <v>39</v>
       </c>
       <c r="D41" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F41:Y41,"P")/(COUNTIF(F41:Y41,"P")+COUNTIF(F41:Y41,"A"))</f>
         <v>0.25</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="1" cm="1">
+        <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>46</v>
+      <c r="G41" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I41" s="1"/>
+      <c r="I41" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2622,10 +2817,11 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y41" s="1"/>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B42" s="1">
@@ -2635,11 +2831,12 @@
         <v>40</v>
       </c>
       <c r="D42" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F42:Y42,"P")/(COUNTIF(F42:Y42,"P")+COUNTIF(F42:Y42,"A"))</f>
         <v>0.25</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>46</v>
+      <c r="E42" s="1" cm="1">
+        <f t="array" ref="E42">_xlfn.IFS(D42&gt;=90%,7.5,D42&gt;=80%,6,D42&gt;=70%,4.5,D42&gt;=60%,3,D42&lt;60%,0)</f>
+        <v>0</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>46</v>
@@ -2647,10 +2844,12 @@
       <c r="G42" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I42" s="1"/>
+      <c r="H42" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2666,10 +2865,11 @@
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y42" s="1"/>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B43" s="1">
@@ -2679,22 +2879,25 @@
         <v>41</v>
       </c>
       <c r="D43" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F43:Y43,"P")/(COUNTIF(F43:Y43,"P")+COUNTIF(F43:Y43,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>47</v>
+      <c r="E43" s="1" cm="1">
+        <f t="array" ref="E43">_xlfn.IFS(D43&gt;=90%,7.5,D43&gt;=80%,6,D43&gt;=70%,4.5,D43&gt;=60%,3,D43&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I43" s="1"/>
+      <c r="I43" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2710,10 +2913,11 @@
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="Y43" s="1"/>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B44" s="1">
@@ -2723,22 +2927,25 @@
         <v>42</v>
       </c>
       <c r="D44" s="8">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(F44:Y44,"P")/(COUNTIF(F44:Y44,"P")+COUNTIF(F44:Y44,"A"))</f>
         <v>0.75</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>47</v>
+      <c r="E44" s="1" cm="1">
+        <f t="array" ref="E44">_xlfn.IFS(D44&gt;=90%,7.5,D44&gt;=80%,6,D44&gt;=70%,4.5,D44&gt;=60%,3,D44&lt;60%,0)</f>
+        <v>4.5</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2754,21 +2961,34 @@
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D44">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="between">
       <formula>0.6</formula>
       <formula>0.89</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E44">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+      <formula>2</formula>
+      <formula>5.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E24F88A-1E57-438C-9F8E-D0E331393B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834D9198-6777-4C6C-9CA7-A669F44BB214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="64">
   <si>
     <t>SL</t>
   </si>
@@ -459,6 +459,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -468,7 +469,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -818,7 +818,7 @@
     <col min="2" max="2" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="21"/>
+    <col min="5" max="5" width="8.88671875" style="18"/>
     <col min="6" max="7" width="27.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="25" width="30.77734375" style="2" customWidth="1"/>
@@ -826,10 +826,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -1007,12 +1007,12 @@
         <v>3</v>
       </c>
       <c r="D4" s="8">
-        <f>COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" ref="D4:D44" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
+        <v>0.8</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>46</v>
@@ -1026,7 +1026,9 @@
       <c r="I4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1055,12 +1057,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="8">
-        <f>COUNTIF(F5:Y5,"P")/(COUNTIF(F5:Y5,"P")+COUNTIF(F5:Y5,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>47</v>
@@ -1074,7 +1076,9 @@
       <c r="I5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -1093,7 +1097,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A44" si="1">A5+1</f>
+        <f t="shared" ref="A6:A44" si="2">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="1">
@@ -1103,12 +1107,12 @@
         <v>5</v>
       </c>
       <c r="D6" s="8">
-        <f>COUNTIF(F6:Y6,"P")/(COUNTIF(F6:Y6,"P")+COUNTIF(F6:Y6,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>47</v>
@@ -1122,7 +1126,9 @@
       <c r="I6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1141,7 +1147,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="B7" s="1">
@@ -1151,7 +1157,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="8">
-        <f>COUNTIF(F7:Y7,"P")/(COUNTIF(F7:Y7,"P")+COUNTIF(F7:Y7,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E7" s="1" cm="1">
@@ -1170,7 +1176,9 @@
       <c r="I7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -1189,7 +1197,7 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -1199,7 +1207,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="8">
-        <f>COUNTIF(F8:Y8,"P")/(COUNTIF(F8:Y8,"P")+COUNTIF(F8:Y8,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E8" s="1" cm="1">
@@ -1218,7 +1226,9 @@
       <c r="I8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -1237,7 +1247,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="B9" s="1">
@@ -1247,12 +1257,12 @@
         <v>8</v>
       </c>
       <c r="D9" s="8">
-        <f>COUNTIF(F9:Y9,"P")/(COUNTIF(F9:Y9,"P")+COUNTIF(F9:Y9,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>47</v>
@@ -1266,7 +1276,9 @@
       <c r="I9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1285,7 +1297,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="B10" s="1">
@@ -1295,12 +1307,12 @@
         <v>9</v>
       </c>
       <c r="D10" s="8">
-        <f>COUNTIF(F10:Y10,"P")/(COUNTIF(F10:Y10,"P")+COUNTIF(F10:Y10,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>47</v>
@@ -1314,7 +1326,9 @@
       <c r="I10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1333,7 +1347,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B11" s="1">
@@ -1343,7 +1357,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="8">
-        <f>COUNTIF(F11:Y11,"P")/(COUNTIF(F11:Y11,"P")+COUNTIF(F11:Y11,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E11" s="1" cm="1">
@@ -1362,7 +1376,9 @@
       <c r="I11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1381,7 +1397,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B12" s="1">
@@ -1391,12 +1407,12 @@
         <v>11</v>
       </c>
       <c r="D12" s="8">
-        <f>COUNTIF(F12:Y12,"P")/(COUNTIF(F12:Y12,"P")+COUNTIF(F12:Y12,"A"))</f>
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E12" s="1" cm="1">
         <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>46</v>
@@ -1410,7 +1426,9 @@
       <c r="I12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -1429,7 +1447,7 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B13" s="1">
@@ -1439,7 +1457,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="8">
-        <f>COUNTIF(F13:Y13,"P")/(COUNTIF(F13:Y13,"P")+COUNTIF(F13:Y13,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E13" s="1" cm="1">
@@ -1458,7 +1476,9 @@
       <c r="I13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1477,7 +1497,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B14" s="1">
@@ -1487,12 +1507,12 @@
         <v>13</v>
       </c>
       <c r="D14" s="8">
-        <f>COUNTIF(F14:Y14,"P")/(COUNTIF(F14:Y14,"P")+COUNTIF(F14:Y14,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>46</v>
@@ -1506,7 +1526,9 @@
       <c r="I14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1525,7 +1547,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B15" s="1">
@@ -1535,7 +1557,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="8">
-        <f>COUNTIF(F15:Y15,"P")/(COUNTIF(F15:Y15,"P")+COUNTIF(F15:Y15,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E15" s="1" cm="1">
@@ -1554,7 +1576,9 @@
       <c r="I15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1573,7 +1597,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B16" s="1">
@@ -1583,7 +1607,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="8">
-        <f>COUNTIF(F16:Y16,"P")/(COUNTIF(F16:Y16,"P")+COUNTIF(F16:Y16,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E16" s="1" cm="1">
@@ -1602,7 +1626,9 @@
       <c r="I16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1621,7 +1647,7 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B17" s="1">
@@ -1631,12 +1657,12 @@
         <v>16</v>
       </c>
       <c r="D17" s="8">
-        <f>COUNTIF(F17:Y17,"P")/(COUNTIF(F17:Y17,"P")+COUNTIF(F17:Y17,"A"))</f>
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>47</v>
@@ -1650,7 +1676,9 @@
       <c r="I17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1669,7 +1697,7 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B18" s="1">
@@ -1679,7 +1707,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="8">
-        <f>COUNTIF(F18:Y18,"P")/(COUNTIF(F18:Y18,"P")+COUNTIF(F18:Y18,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E18" s="1" cm="1">
@@ -1698,7 +1726,9 @@
       <c r="I18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1717,7 +1747,7 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B19" s="1">
@@ -1727,12 +1757,12 @@
         <v>18</v>
       </c>
       <c r="D19" s="8">
-        <f>COUNTIF(F19:Y19,"P")/(COUNTIF(F19:Y19,"P")+COUNTIF(F19:Y19,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>47</v>
@@ -1746,7 +1776,9 @@
       <c r="I19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="J19" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1765,7 +1797,7 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B20" s="1">
@@ -1775,7 +1807,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="8">
-        <f>COUNTIF(F20:Y20,"P")/(COUNTIF(F20:Y20,"P")+COUNTIF(F20:Y20,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E20" s="1" cm="1">
@@ -1794,7 +1826,9 @@
       <c r="I20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1813,7 +1847,7 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B21" s="1">
@@ -1823,7 +1857,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIF(F21:Y21,"P")/(COUNTIF(F21:Y21,"P")+COUNTIF(F21:Y21,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E21" s="1" cm="1">
@@ -1842,7 +1876,9 @@
       <c r="I21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -1861,7 +1897,7 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="B22" s="1">
@@ -1871,7 +1907,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="8">
-        <f>COUNTIF(F22:Y22,"P")/(COUNTIF(F22:Y22,"P")+COUNTIF(F22:Y22,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E22" s="1" cm="1">
@@ -1890,7 +1926,9 @@
       <c r="I22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1909,7 +1947,7 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B23" s="1">
@@ -1919,12 +1957,12 @@
         <v>22</v>
       </c>
       <c r="D23" s="8">
-        <f>COUNTIF(F23:Y23,"P")/(COUNTIF(F23:Y23,"P")+COUNTIF(F23:Y23,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>47</v>
@@ -1938,7 +1976,9 @@
       <c r="I23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1957,7 +1997,7 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B24" s="1">
@@ -1967,12 +2007,12 @@
         <v>23</v>
       </c>
       <c r="D24" s="8">
-        <f>COUNTIF(F24:Y24,"P")/(COUNTIF(F24:Y24,"P")+COUNTIF(F24:Y24,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>47</v>
@@ -1986,7 +2026,9 @@
       <c r="I24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2005,7 +2047,7 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B25" s="1">
@@ -2015,12 +2057,12 @@
         <v>24</v>
       </c>
       <c r="D25" s="8">
-        <f>COUNTIF(F25:Y25,"P")/(COUNTIF(F25:Y25,"P")+COUNTIF(F25:Y25,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>46</v>
@@ -2034,7 +2076,9 @@
       <c r="I25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2053,7 +2097,7 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B26" s="1">
@@ -2063,7 +2107,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="8">
-        <f>COUNTIF(F26:Y26,"P")/(COUNTIF(F26:Y26,"P")+COUNTIF(F26:Y26,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E26" s="1" cm="1">
@@ -2082,7 +2126,9 @@
       <c r="I26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -2101,7 +2147,7 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="B27" s="1">
@@ -2111,7 +2157,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="8">
-        <f>COUNTIF(F27:Y27,"P")/(COUNTIF(F27:Y27,"P")+COUNTIF(F27:Y27,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E27" s="1" cm="1">
@@ -2130,7 +2176,9 @@
       <c r="I27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -2149,7 +2197,7 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B28" s="1">
@@ -2159,7 +2207,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="8">
-        <f>COUNTIF(F28:Y28,"P")/(COUNTIF(F28:Y28,"P")+COUNTIF(F28:Y28,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E28" s="1" cm="1">
@@ -2178,7 +2226,9 @@
       <c r="I28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -2197,7 +2247,7 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B29" s="1">
@@ -2207,7 +2257,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="8">
-        <f>COUNTIF(F29:Y29,"P")/(COUNTIF(F29:Y29,"P")+COUNTIF(F29:Y29,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E29" s="1" cm="1">
@@ -2226,7 +2276,9 @@
       <c r="I29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2245,7 +2297,7 @@
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="B30" s="1">
@@ -2255,7 +2307,7 @@
         <v>29</v>
       </c>
       <c r="D30" s="8">
-        <f>COUNTIF(F30:Y30,"P")/(COUNTIF(F30:Y30,"P")+COUNTIF(F30:Y30,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E30" s="1" cm="1">
@@ -2274,7 +2326,9 @@
       <c r="I30" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2293,7 +2347,7 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="B31" s="1">
@@ -2303,12 +2357,12 @@
         <v>30</v>
       </c>
       <c r="D31" s="8">
-        <f>COUNTIF(F31:Y31,"P")/(COUNTIF(F31:Y31,"P")+COUNTIF(F31:Y31,"A"))</f>
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>47</v>
@@ -2322,7 +2376,9 @@
       <c r="I31" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -2341,7 +2397,7 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="B32" s="1">
@@ -2351,12 +2407,12 @@
         <v>31</v>
       </c>
       <c r="D32" s="8">
-        <f>COUNTIF(F32:Y32,"P")/(COUNTIF(F32:Y32,"P")+COUNTIF(F32:Y32,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>47</v>
@@ -2370,7 +2426,9 @@
       <c r="I32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -2389,7 +2447,7 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="B33" s="1">
@@ -2399,7 +2457,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="8">
-        <f>COUNTIF(F33:Y33,"P")/(COUNTIF(F33:Y33,"P")+COUNTIF(F33:Y33,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E33" s="1" cm="1">
@@ -2418,7 +2476,9 @@
       <c r="I33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2437,7 +2497,7 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="B34" s="1">
@@ -2447,7 +2507,7 @@
         <v>33</v>
       </c>
       <c r="D34" s="8">
-        <f>COUNTIF(F34:Y34,"P")/(COUNTIF(F34:Y34,"P")+COUNTIF(F34:Y34,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E34" s="1" cm="1">
@@ -2466,7 +2526,9 @@
       <c r="I34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J34" s="1"/>
+      <c r="J34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2485,7 +2547,7 @@
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="B35" s="1">
@@ -2495,12 +2557,12 @@
         <v>34</v>
       </c>
       <c r="D35" s="8">
-        <f>COUNTIF(F35:Y35,"P")/(COUNTIF(F35:Y35,"P")+COUNTIF(F35:Y35,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>47</v>
@@ -2514,7 +2576,9 @@
       <c r="I35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2533,7 +2597,7 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="B36" s="11">
@@ -2543,7 +2607,7 @@
         <v>35</v>
       </c>
       <c r="D36" s="8">
-        <f>COUNTIF(F36:Y36,"P")/(COUNTIF(F36:Y36,"P")+COUNTIF(F36:Y36,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E36" s="1" cm="1">
@@ -2562,7 +2626,9 @@
       <c r="I36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J36" s="1"/>
+      <c r="J36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -2581,7 +2647,7 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="B37" s="1">
@@ -2591,7 +2657,7 @@
         <v>36</v>
       </c>
       <c r="D37" s="8">
-        <f>COUNTIF(F37:Y37,"P")/(COUNTIF(F37:Y37,"P")+COUNTIF(F37:Y37,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E37" s="1" cm="1">
@@ -2610,7 +2676,9 @@
       <c r="I37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2629,7 +2697,7 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="B38" s="1">
@@ -2639,7 +2707,7 @@
         <v>37</v>
       </c>
       <c r="D38" s="8">
-        <f>COUNTIF(F38:Y38,"P")/(COUNTIF(F38:Y38,"P")+COUNTIF(F38:Y38,"A"))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E38" s="1" cm="1">
@@ -2658,7 +2726,9 @@
       <c r="I38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2677,7 +2747,7 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="B39" s="1">
@@ -2687,8 +2757,8 @@
         <v>50</v>
       </c>
       <c r="D39" s="8">
-        <f>COUNTIF(F39:Y39,"P")/(COUNTIF(F39:Y39,"P")+COUNTIF(F39:Y39,"A"))</f>
-        <v>0.25</v>
+        <f t="shared" si="1"/>
+        <v>0.2</v>
       </c>
       <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
@@ -2706,7 +2776,9 @@
       <c r="I39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J39" s="1"/>
+      <c r="J39" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2725,7 +2797,7 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="B40" s="1">
@@ -2735,12 +2807,12 @@
         <v>38</v>
       </c>
       <c r="D40" s="8">
-        <f>COUNTIF(F40:Y40,"P")/(COUNTIF(F40:Y40,"P")+COUNTIF(F40:Y40,"A"))</f>
-        <v>0.5</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>47</v>
@@ -2754,7 +2826,9 @@
       <c r="I40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2773,7 +2847,7 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="B41" s="1">
@@ -2783,8 +2857,8 @@
         <v>39</v>
       </c>
       <c r="D41" s="8">
-        <f>COUNTIF(F41:Y41,"P")/(COUNTIF(F41:Y41,"P")+COUNTIF(F41:Y41,"A"))</f>
-        <v>0.25</v>
+        <f t="shared" si="1"/>
+        <v>0.2</v>
       </c>
       <c r="E41" s="1" cm="1">
         <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
@@ -2802,7 +2876,9 @@
       <c r="I41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J41" s="1"/>
+      <c r="J41" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -2821,7 +2897,7 @@
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="B42" s="1">
@@ -2831,8 +2907,8 @@
         <v>40</v>
       </c>
       <c r="D42" s="8">
-        <f>COUNTIF(F42:Y42,"P")/(COUNTIF(F42:Y42,"P")+COUNTIF(F42:Y42,"A"))</f>
-        <v>0.25</v>
+        <f t="shared" si="1"/>
+        <v>0.4</v>
       </c>
       <c r="E42" s="1" cm="1">
         <f t="array" ref="E42">_xlfn.IFS(D42&gt;=90%,7.5,D42&gt;=80%,6,D42&gt;=70%,4.5,D42&gt;=60%,3,D42&lt;60%,0)</f>
@@ -2850,7 +2926,9 @@
       <c r="I42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -2869,7 +2947,7 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="B43" s="1">
@@ -2879,12 +2957,12 @@
         <v>41</v>
       </c>
       <c r="D43" s="8">
-        <f>COUNTIF(F43:Y43,"P")/(COUNTIF(F43:Y43,"P")+COUNTIF(F43:Y43,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.6</v>
       </c>
       <c r="E43" s="1" cm="1">
         <f t="array" ref="E43">_xlfn.IFS(D43&gt;=90%,7.5,D43&gt;=80%,6,D43&gt;=70%,4.5,D43&gt;=60%,3,D43&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>47</v>
@@ -2898,7 +2976,9 @@
       <c r="I43" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J43" s="1"/>
+      <c r="J43" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2917,7 +2997,7 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="B44" s="1">
@@ -2927,12 +3007,12 @@
         <v>42</v>
       </c>
       <c r="D44" s="8">
-        <f>COUNTIF(F44:Y44,"P")/(COUNTIF(F44:Y44,"P")+COUNTIF(F44:Y44,"A"))</f>
-        <v>0.75</v>
+        <f t="shared" si="1"/>
+        <v>0.8</v>
       </c>
       <c r="E44" s="1" cm="1">
         <f t="array" ref="E44">_xlfn.IFS(D44&gt;=90%,7.5,D44&gt;=80%,6,D44&gt;=70%,4.5,D44&gt;=60%,3,D44&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>47</v>
@@ -2946,7 +3026,9 @@
       <c r="I44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -3014,10 +3096,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -3030,17 +3112,17 @@
       <c r="F1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="20" t="s">
+      <c r="H1" s="20"/>
+      <c r="I1" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="21" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3064,11 +3146,11 @@
       <c r="F2" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -3096,9 +3178,9 @@
       <c r="H3" s="13">
         <v>7.5</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">

--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834D9198-6777-4C6C-9CA7-A669F44BB214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A9D168-6451-49E1-B5C0-3410C89BB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="64">
   <si>
     <t>SL</t>
   </si>
@@ -474,7 +474,7 @@
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -522,6 +522,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -821,7 +841,10 @@
     <col min="5" max="5" width="8.88671875" style="18"/>
     <col min="6" max="7" width="27.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="34.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="25" width="30.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="30.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="36.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="30.77734375" style="2" customWidth="1"/>
     <col min="26" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
@@ -980,8 +1003,12 @@
       <c r="J3" s="9">
         <v>46278</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
+      <c r="K3" s="9">
+        <v>46281</v>
+      </c>
+      <c r="L3" s="9">
+        <v>46285</v>
+      </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
@@ -1008,7 +1035,7 @@
       </c>
       <c r="D4" s="8">
         <f t="shared" ref="D4:D44" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1029,8 +1056,12 @@
       <c r="J4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -1058,7 +1089,7 @@
       </c>
       <c r="D5" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1079,8 +1110,12 @@
       <c r="J5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -1108,11 +1143,11 @@
       </c>
       <c r="D6" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>47</v>
@@ -1129,8 +1164,12 @@
       <c r="J6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -1179,8 +1218,12 @@
       <c r="J7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1229,8 +1272,12 @@
       <c r="J8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -1258,11 +1305,11 @@
       </c>
       <c r="D9" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>47</v>
@@ -1279,8 +1326,12 @@
       <c r="J9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1308,11 +1359,11 @@
       </c>
       <c r="D10" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>47</v>
@@ -1329,8 +1380,12 @@
       <c r="J10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1379,8 +1434,12 @@
       <c r="J11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1408,11 +1467,11 @@
       </c>
       <c r="D12" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E12" s="1" cm="1">
         <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>46</v>
@@ -1429,8 +1488,12 @@
       <c r="J12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="K12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1479,8 +1542,12 @@
       <c r="J13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1508,11 +1575,11 @@
       </c>
       <c r="D14" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>46</v>
@@ -1529,8 +1596,12 @@
       <c r="J14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="K14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -1579,8 +1650,12 @@
       <c r="J15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -1629,8 +1704,12 @@
       <c r="J16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="K16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -1658,11 +1737,11 @@
       </c>
       <c r="D17" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>47</v>
@@ -1679,8 +1758,12 @@
       <c r="J17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="K17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -1729,8 +1812,12 @@
       <c r="J18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="K18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -1758,11 +1845,11 @@
       </c>
       <c r="D19" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>47</v>
@@ -1779,8 +1866,12 @@
       <c r="J19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1808,11 +1899,11 @@
       </c>
       <c r="D20" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>47</v>
@@ -1829,8 +1920,12 @@
       <c r="J20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="K20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -1879,8 +1974,12 @@
       <c r="J21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="K21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -1929,8 +2028,12 @@
       <c r="J22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="K22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -1958,7 +2061,7 @@
       </c>
       <c r="D23" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -1979,8 +2082,12 @@
       <c r="J23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -2008,11 +2115,11 @@
       </c>
       <c r="D24" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>47</v>
@@ -2029,8 +2136,12 @@
       <c r="J24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="K24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -2058,7 +2169,7 @@
       </c>
       <c r="D25" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2079,8 +2190,12 @@
       <c r="J25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="K25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -2108,11 +2223,11 @@
       </c>
       <c r="D26" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>47</v>
@@ -2129,8 +2244,12 @@
       <c r="J26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+      <c r="K26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -2179,8 +2298,12 @@
       <c r="J27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
+      <c r="K27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -2208,11 +2331,11 @@
       </c>
       <c r="D28" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>47</v>
@@ -2229,8 +2352,12 @@
       <c r="J28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
+      <c r="K28" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -2279,8 +2406,12 @@
       <c r="J29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
+      <c r="K29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -2329,8 +2460,12 @@
       <c r="J30" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="K30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -2358,11 +2493,11 @@
       </c>
       <c r="D31" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>47</v>
@@ -2379,8 +2514,12 @@
       <c r="J31" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
+      <c r="K31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -2408,11 +2547,11 @@
       </c>
       <c r="D32" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>47</v>
@@ -2429,8 +2568,12 @@
       <c r="J32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
+      <c r="K32" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -2479,8 +2622,12 @@
       <c r="J33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -2529,8 +2676,12 @@
       <c r="J34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
+      <c r="K34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -2558,11 +2709,11 @@
       </c>
       <c r="D35" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>47</v>
@@ -2579,8 +2730,12 @@
       <c r="J35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
+      <c r="K35" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
@@ -2608,11 +2763,11 @@
       </c>
       <c r="D36" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>47</v>
@@ -2629,8 +2784,12 @@
       <c r="J36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="K36" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -2679,8 +2838,12 @@
       <c r="J37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
@@ -2708,11 +2871,11 @@
       </c>
       <c r="D38" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E38" s="1" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>47</v>
@@ -2729,8 +2892,12 @@
       <c r="J38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="K38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -2758,7 +2925,7 @@
       </c>
       <c r="D39" s="8">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
@@ -2779,8 +2946,12 @@
       <c r="J39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="K39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
@@ -2808,11 +2979,11 @@
       </c>
       <c r="D40" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>47</v>
@@ -2829,8 +3000,12 @@
       <c r="J40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="K40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -2858,7 +3033,7 @@
       </c>
       <c r="D41" s="8">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E41" s="1" cm="1">
         <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
@@ -2879,8 +3054,12 @@
       <c r="J41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="K41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
@@ -2908,7 +3087,7 @@
       </c>
       <c r="D42" s="8">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E42" s="1" cm="1">
         <f t="array" ref="E42">_xlfn.IFS(D42&gt;=90%,7.5,D42&gt;=80%,6,D42&gt;=70%,4.5,D42&gt;=60%,3,D42&lt;60%,0)</f>
@@ -2929,8 +3108,12 @@
       <c r="J42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="K42" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -2958,11 +3141,11 @@
       </c>
       <c r="D43" s="8">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E43" s="1" cm="1">
         <f t="array" ref="E43">_xlfn.IFS(D43&gt;=90%,7.5,D43&gt;=80%,6,D43&gt;=70%,4.5,D43&gt;=60%,3,D43&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>47</v>
@@ -2979,8 +3162,12 @@
       <c r="J43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
+      <c r="K43" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -3008,11 +3195,11 @@
       </c>
       <c r="D44" s="8">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E44" s="1" cm="1">
         <f t="array" ref="E44">_xlfn.IFS(D44&gt;=90%,7.5,D44&gt;=80%,6,D44&gt;=70%,4.5,D44&gt;=60%,3,D44&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>47</v>
@@ -3029,8 +3216,12 @@
       <c r="J44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="K44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
@@ -3050,26 +3241,33 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D44">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="between">
+      <formula>0.6</formula>
+      <formula>0.79</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+      <formula>0.79</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
       <formula>0.6</formula>
       <formula>0.89</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E44">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="lessThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="between">
       <formula>2</formula>
       <formula>5.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A9D168-6451-49E1-B5C0-3410C89BB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A33129-78C3-4CEF-9E57-B29E2E7530D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESE 2-1 Attendance" sheetId="1" r:id="rId1"/>
-    <sheet name="Assessment" sheetId="8" r:id="rId2"/>
+    <sheet name="Assignment" sheetId="8" r:id="rId2"/>
+    <sheet name="Class Test" sheetId="9" r:id="rId3"/>
+    <sheet name="Eval." sheetId="10" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assessment!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ESE 2-1 Attendance'!$F$3:$Y$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Assignment!$A$1:$I$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Class Test'!$A$1:$D$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ESE 2-1 Attendance'!$F$3:$T$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Eval.!$A$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="72">
   <si>
     <t>SL</t>
   </si>
@@ -222,9 +226,6 @@
     <t>Assignmnet 2</t>
   </si>
   <si>
-    <t>Assignment 3</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -237,22 +238,49 @@
     <t>Comments on 1st Assignemnt</t>
   </si>
   <si>
-    <t>COPY</t>
-  </si>
-  <si>
     <t>Comments on 2nd Assignemnt</t>
   </si>
   <si>
-    <t>Comments on 3rd Assignemnt</t>
-  </si>
-  <si>
-    <t>Warp Knitting Lapping</t>
-  </si>
-  <si>
     <t>Held, Tuck Loop</t>
   </si>
   <si>
     <t>Marks</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures &amp; Not Clear</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures</t>
+  </si>
+  <si>
+    <t>Not Submitted</t>
+  </si>
+  <si>
+    <t>Omitted some actions</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures &amp; Omitted some actions</t>
+  </si>
+  <si>
+    <t>NOAS</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>NOCT</t>
+  </si>
+  <si>
+    <t>BOEV</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>Class Test</t>
   </si>
 </sst>
 </file>
@@ -263,7 +291,7 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,8 +338,22 @@
       <name val="Gill Sans MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,8 +419,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -401,12 +473,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -460,6 +569,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -468,6 +592,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -831,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
@@ -844,15 +992,15 @@
     <col min="10" max="10" width="30.77734375" style="2" customWidth="1"/>
     <col min="11" max="11" width="36.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="25" width="30.77734375" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="2"/>
+    <col min="13" max="20" width="30.77734375" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="24"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -873,13 +1021,8 @@
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
       <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -900,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6">
-        <f t="shared" ref="H2:Y2" si="0">G2+1</f>
+        <f t="shared" ref="H2:T2" si="0">G2+1</f>
         <v>3</v>
       </c>
       <c r="I2" s="6">
@@ -951,28 +1094,8 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="U2" s="6">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="V2" s="6">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="W2" s="6">
-        <f>V2+1</f>
-        <v>18</v>
-      </c>
-      <c r="X2" s="6">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="Y2" s="6">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -986,7 +1109,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F3" s="9">
         <v>46257</v>
@@ -1009,7 +1132,9 @@
       <c r="L3" s="9">
         <v>46285</v>
       </c>
-      <c r="M3" s="9"/>
+      <c r="M3" s="9">
+        <v>46292</v>
+      </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -1017,13 +1142,8 @@
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1034,8 +1154,8 @@
         <v>3</v>
       </c>
       <c r="D4" s="8">
-        <f t="shared" ref="D4:D44" si="1">COUNTIF(F4:Y4,"P")/(COUNTIF(F4:Y4,"P")+COUNTIF(F4:Y4,"A"))</f>
-        <v>0.8571428571428571</v>
+        <f t="shared" ref="D4:D44" si="1">COUNTIF(F4:T4,"P")/(COUNTIF(F4:T4,"P")+COUNTIF(F4:T4,"A"))</f>
+        <v>0.875</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1062,7 +1182,9 @@
       <c r="L4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -1070,13 +1192,8 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <f>A4+1</f>
         <v>2</v>
@@ -1089,7 +1206,7 @@
       </c>
       <c r="D5" s="8">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1116,7 +1233,9 @@
       <c r="L5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1124,13 +1243,8 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A44" si="2">A5+1</f>
         <v>3</v>
@@ -1143,7 +1257,7 @@
       </c>
       <c r="D6" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1170,7 +1284,9 @@
       <c r="L6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1178,13 +1294,8 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -1224,7 +1335,9 @@
       <c r="L7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1232,13 +1345,8 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -1278,7 +1386,9 @@
       <c r="L8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1286,13 +1396,8 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -1305,7 +1410,7 @@
       </c>
       <c r="D9" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1332,7 +1437,9 @@
       <c r="L9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1340,13 +1447,8 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -1359,7 +1461,7 @@
       </c>
       <c r="D10" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1386,7 +1488,9 @@
       <c r="L10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1394,13 +1498,8 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -1440,7 +1539,9 @@
       <c r="L11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
@@ -1448,13 +1549,8 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -1467,7 +1563,7 @@
       </c>
       <c r="D12" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E12" s="1" cm="1">
         <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
@@ -1494,7 +1590,9 @@
       <c r="L12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -1502,13 +1600,8 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -1548,7 +1641,9 @@
       <c r="L13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
@@ -1556,13 +1651,8 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -1575,11 +1665,11 @@
       </c>
       <c r="D14" s="8">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>46</v>
@@ -1602,7 +1692,9 @@
       <c r="L14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
@@ -1610,13 +1702,8 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -1656,7 +1743,9 @@
       <c r="L15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
@@ -1664,13 +1753,8 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -1710,7 +1794,9 @@
       <c r="L16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
@@ -1718,13 +1804,8 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -1737,7 +1818,7 @@
       </c>
       <c r="D17" s="8">
         <f t="shared" si="1"/>
-        <v>0.42857142857142855</v>
+        <v>0.375</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
@@ -1764,7 +1845,9 @@
       <c r="L17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M17" s="1"/>
+      <c r="M17" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
@@ -1772,13 +1855,8 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1804,7 +1882,7 @@
         <v>47</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>47</v>
@@ -1818,7 +1896,9 @@
       <c r="L18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -1826,13 +1906,8 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -1845,7 +1920,7 @@
       </c>
       <c r="D19" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1872,7 +1947,9 @@
       <c r="L19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1880,13 +1957,8 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -1899,7 +1971,7 @@
       </c>
       <c r="D20" s="8">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -1912,7 +1984,7 @@
         <v>47</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>47</v>
@@ -1926,7 +1998,9 @@
       <c r="L20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
@@ -1934,13 +2008,8 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -1966,7 +2035,7 @@
         <v>47</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>47</v>
@@ -1980,7 +2049,9 @@
       <c r="L21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
@@ -1988,13 +2059,8 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -2020,7 +2086,7 @@
         <v>47</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>47</v>
@@ -2034,7 +2100,9 @@
       <c r="L22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -2042,13 +2110,8 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -2061,7 +2124,7 @@
       </c>
       <c r="D23" s="8">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2074,7 +2137,7 @@
         <v>46</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>47</v>
@@ -2088,7 +2151,9 @@
       <c r="L23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
@@ -2096,13 +2161,8 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -2115,7 +2175,7 @@
       </c>
       <c r="D24" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
@@ -2128,7 +2188,7 @@
         <v>46</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>47</v>
@@ -2142,7 +2202,9 @@
       <c r="L24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -2150,13 +2212,8 @@
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2169,7 +2226,7 @@
       </c>
       <c r="D25" s="8">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
@@ -2182,7 +2239,7 @@
         <v>47</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>47</v>
@@ -2196,7 +2253,9 @@
       <c r="L25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -2204,13 +2263,8 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2223,7 +2277,7 @@
       </c>
       <c r="D26" s="8">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2236,7 +2290,7 @@
         <v>47</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>47</v>
@@ -2250,7 +2304,9 @@
       <c r="L26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -2258,13 +2314,8 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2290,7 +2341,7 @@
         <v>47</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>47</v>
@@ -2304,7 +2355,9 @@
       <c r="L27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -2312,13 +2365,8 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2331,7 +2379,7 @@
       </c>
       <c r="D28" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
@@ -2344,7 +2392,7 @@
         <v>47</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>47</v>
@@ -2358,7 +2406,9 @@
       <c r="L28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
@@ -2366,13 +2416,8 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2398,7 +2443,7 @@
         <v>47</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>47</v>
@@ -2412,7 +2457,9 @@
       <c r="L29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -2420,13 +2467,8 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2452,7 +2494,7 @@
         <v>47</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>47</v>
@@ -2466,7 +2508,9 @@
       <c r="L30" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2474,13 +2518,8 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="16">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2493,11 +2532,11 @@
       </c>
       <c r="D31" s="8">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>47</v>
@@ -2520,7 +2559,9 @@
       <c r="L31" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
@@ -2528,13 +2569,8 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2547,11 +2583,11 @@
       </c>
       <c r="D32" s="8">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>47</v>
@@ -2574,7 +2610,9 @@
       <c r="L32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M32" s="1"/>
+      <c r="M32" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
@@ -2582,13 +2620,8 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2628,7 +2661,9 @@
       <c r="L33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -2636,13 +2671,8 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2682,7 +2712,9 @@
       <c r="L34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M34" s="1"/>
+      <c r="M34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -2690,13 +2722,8 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2709,7 +2736,7 @@
       </c>
       <c r="D35" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
@@ -2736,7 +2763,9 @@
       <c r="L35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M35" s="1"/>
+      <c r="M35" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
@@ -2744,13 +2773,8 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2763,7 +2787,7 @@
       </c>
       <c r="D36" s="8">
         <f t="shared" si="1"/>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
@@ -2790,7 +2814,9 @@
       <c r="L36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M36" s="1"/>
+      <c r="M36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
@@ -2798,13 +2824,8 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2844,7 +2865,9 @@
       <c r="L37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M37" s="1"/>
+      <c r="M37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
@@ -2852,13 +2875,8 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -2871,7 +2889,7 @@
       </c>
       <c r="D38" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="E38" s="1" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
@@ -2898,7 +2916,9 @@
       <c r="L38" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M38" s="1"/>
+      <c r="M38" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -2906,13 +2926,8 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -2925,7 +2940,7 @@
       </c>
       <c r="D39" s="8">
         <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
@@ -2952,7 +2967,9 @@
       <c r="L39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M39" s="1"/>
+      <c r="M39" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
@@ -2960,13 +2977,8 @@
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -2979,7 +2991,7 @@
       </c>
       <c r="D40" s="8">
         <f t="shared" si="1"/>
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
@@ -3006,7 +3018,9 @@
       <c r="L40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M40" s="1"/>
+      <c r="M40" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -3014,13 +3028,8 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -3033,7 +3042,7 @@
       </c>
       <c r="D41" s="8">
         <f t="shared" si="1"/>
-        <v>0.14285714285714285</v>
+        <v>0.125</v>
       </c>
       <c r="E41" s="1" cm="1">
         <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
@@ -3060,7 +3069,9 @@
       <c r="L41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M41" s="1"/>
+      <c r="M41" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -3068,13 +3079,8 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -3087,7 +3093,7 @@
       </c>
       <c r="D42" s="8">
         <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="E42" s="1" cm="1">
         <f t="array" ref="E42">_xlfn.IFS(D42&gt;=90%,7.5,D42&gt;=80%,6,D42&gt;=70%,4.5,D42&gt;=60%,3,D42&lt;60%,0)</f>
@@ -3114,7 +3120,9 @@
       <c r="L42" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M42" s="1"/>
+      <c r="M42" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -3122,13 +3130,8 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -3141,7 +3144,7 @@
       </c>
       <c r="D43" s="8">
         <f t="shared" si="1"/>
-        <v>0.42857142857142855</v>
+        <v>0.375</v>
       </c>
       <c r="E43" s="1" cm="1">
         <f t="array" ref="E43">_xlfn.IFS(D43&gt;=90%,7.5,D43&gt;=80%,6,D43&gt;=70%,4.5,D43&gt;=60%,3,D43&lt;60%,0)</f>
@@ -3168,7 +3171,9 @@
       <c r="L43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M43" s="1"/>
+      <c r="M43" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -3176,13 +3181,8 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -3195,11 +3195,11 @@
       </c>
       <c r="D44" s="8">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="E44" s="1" cm="1">
         <f t="array" ref="E44">_xlfn.IFS(D44&gt;=90%,7.5,D44&gt;=80%,6,D44&gt;=70%,4.5,D44&gt;=60%,3,D44&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>47</v>
@@ -3222,7 +3222,9 @@
       <c r="L44" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M44" s="1"/>
+      <c r="M44" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -3230,11 +3232,6 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3278,7 +3275,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A46F8F3-1BFE-4AF0-A2BB-D8B7450A48F3}">
-  <dimension ref="A1:K44"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
@@ -3286,18 +3286,18 @@
     <col min="3" max="3" width="49.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="11" style="2" customWidth="1"/>
-    <col min="9" max="11" width="27.77734375" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="2"/>
+    <col min="6" max="6" width="8.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="24"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -3307,24 +3307,18 @@
       <c r="E1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="21" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -3333,24 +3327,20 @@
         <v>41</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="28"/>
+    </row>
+    <row r="3" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -3366,21 +3356,17 @@
       <c r="E3" s="15">
         <v>7.5</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="13">
+        <f t="shared" ref="F3:F44" si="0">SUM(D3:E3)</f>
+        <v>15</v>
+      </c>
+      <c r="G3" s="13">
         <v>7.5</v>
       </c>
-      <c r="G3" s="13">
-        <f t="shared" ref="G3:G44" si="0">SUM(D3:F3)</f>
-        <v>22.5</v>
-      </c>
-      <c r="H3" s="13">
-        <v>7.5</v>
-      </c>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H3" s="26"/>
+      <c r="I3" s="29"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3391,28 +3377,28 @@
         <v>3</v>
       </c>
       <c r="D4" s="14">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H4" s="17">
-        <f>G4/3</f>
-        <v>1.6666666666666667</v>
+      <c r="F4" s="14">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+      <c r="G4" s="17">
+        <f>F4/2</f>
+        <v>2.75</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
         <f>A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="20">
         <v>25011001003</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3422,20 +3408,18 @@
         <v>7</v>
       </c>
       <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14">
+      <c r="F5" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H5" s="17">
-        <f t="shared" ref="H5:H44" si="1">G5/3</f>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G5" s="17">
+        <f t="shared" ref="G5:G44" si="1">F5/2</f>
+        <v>3.5</v>
+      </c>
+      <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A44" si="2">A5+1</f>
         <v>3</v>
@@ -3450,20 +3434,18 @@
         <v>6</v>
       </c>
       <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14">
+      <c r="F6" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H6" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="G6" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -3475,25 +3457,23 @@
         <v>6</v>
       </c>
       <c r="D7" s="14">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H7" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F7" s="14">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G7" s="17">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -3508,20 +3488,18 @@
         <v>7</v>
       </c>
       <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14">
+      <c r="F8" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H8" s="17">
-        <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G8" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -3536,20 +3514,18 @@
         <v>7</v>
       </c>
       <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14">
+      <c r="F9" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H9" s="17">
-        <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G9" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -3564,20 +3540,18 @@
         <v>6.5</v>
       </c>
       <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14">
+      <c r="F10" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H10" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G10" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -3592,20 +3566,18 @@
         <v>7</v>
       </c>
       <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14">
+      <c r="F11" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H11" s="17">
-        <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G11" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -3620,20 +3592,18 @@
         <v>6</v>
       </c>
       <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14">
+      <c r="F12" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H12" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -3648,20 +3618,18 @@
         <v>6.5</v>
       </c>
       <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14">
+      <c r="F13" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H13" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -3676,20 +3644,18 @@
         <v>6.5</v>
       </c>
       <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14">
+      <c r="F14" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H14" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G14" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -3701,25 +3667,23 @@
         <v>14</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H15" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F15" s="14">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G15" s="17">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -3734,20 +3698,18 @@
         <v>7</v>
       </c>
       <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14">
+      <c r="F16" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H16" s="17">
-        <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G16" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -3759,23 +3721,21 @@
         <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14">
-        <f t="shared" si="0"/>
-        <v>5.5</v>
-      </c>
-      <c r="H17" s="17">
-        <f t="shared" si="1"/>
-        <v>1.8333333333333333</v>
-      </c>
+      <c r="F17" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -3790,20 +3750,20 @@
         <v>5.5</v>
       </c>
       <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14">
+      <c r="F18" s="14">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="H18" s="17">
-        <f t="shared" si="1"/>
-        <v>1.8333333333333333</v>
+      <c r="G18" s="17">
+        <f t="shared" si="1"/>
+        <v>2.75</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -3818,20 +3778,18 @@
         <v>6</v>
       </c>
       <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14">
+      <c r="F19" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H19" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="G19" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -3846,20 +3804,18 @@
         <v>6</v>
       </c>
       <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14">
+      <c r="F20" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H20" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="G20" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -3874,20 +3830,18 @@
         <v>6.5</v>
       </c>
       <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14">
+      <c r="F21" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H21" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G21" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>19</v>
@@ -3902,20 +3856,18 @@
         <v>6.5</v>
       </c>
       <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14">
+      <c r="F22" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H22" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G22" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
@@ -3927,25 +3879,23 @@
         <v>22</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H23" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F23" s="14">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G23" s="17">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>21</v>
@@ -3960,20 +3910,18 @@
         <v>7</v>
       </c>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14">
+      <c r="F24" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H24" s="17">
-        <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G24" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -3985,23 +3933,23 @@
         <v>24</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="H25" s="17">
-        <f t="shared" si="1"/>
-        <v>1.3333333333333333</v>
+      <c r="F25" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G25" s="17">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -4016,20 +3964,20 @@
         <v>5.5</v>
       </c>
       <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14">
+      <c r="F26" s="14">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="H26" s="17">
-        <f t="shared" si="1"/>
-        <v>1.8333333333333333</v>
+      <c r="G26" s="17">
+        <f t="shared" si="1"/>
+        <v>2.75</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -4044,20 +3992,18 @@
         <v>7</v>
       </c>
       <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14">
+      <c r="F27" s="14">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H27" s="17">
-        <f t="shared" si="1"/>
-        <v>2.3333333333333335</v>
-      </c>
+      <c r="G27" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -4072,20 +4018,20 @@
         <v>4.5</v>
       </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14">
+      <c r="F28" s="14">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="H28" s="17">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+      <c r="G28" s="17">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -4097,23 +4043,21 @@
         <v>28</v>
       </c>
       <c r="D29" s="14">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14">
-        <f t="shared" si="0"/>
-        <v>6.5</v>
-      </c>
-      <c r="H29" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="F29" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G29" s="17">
+        <f t="shared" si="1"/>
+        <v>3.5</v>
+      </c>
+      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -4128,20 +4072,18 @@
         <v>6</v>
       </c>
       <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14">
+      <c r="F30" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H30" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="G30" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -4153,25 +4095,23 @@
         <v>30</v>
       </c>
       <c r="D31" s="14">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="H31" s="17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F31" s="14">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="G31" s="17">
+        <f t="shared" si="1"/>
+        <v>2.25</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -4183,23 +4123,23 @@
         <v>31</v>
       </c>
       <c r="D32" s="1">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="14">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
-      </c>
-      <c r="H32" s="17">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
+      <c r="F32" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G32" s="17">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -4214,20 +4154,18 @@
         <v>6.5</v>
       </c>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="14">
+      <c r="F33" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H33" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G33" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -4239,23 +4177,21 @@
         <v>33</v>
       </c>
       <c r="D34" s="1">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="14">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="H34" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="F34" s="14">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="G34" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -4270,25 +4206,25 @@
         <v>5</v>
       </c>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="14">
+      <c r="F35" s="14">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="H35" s="17">
-        <f t="shared" si="1"/>
-        <v>1.6666666666666667</v>
+      <c r="G35" s="17">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="11">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="20">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="20">
         <v>25011001038</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -4298,20 +4234,18 @@
         <v>6.5</v>
       </c>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="14">
+      <c r="F36" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H36" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G36" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -4326,20 +4260,18 @@
         <v>6.5</v>
       </c>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="14">
+      <c r="F37" s="14">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="H37" s="17">
-        <f t="shared" si="1"/>
-        <v>2.1666666666666665</v>
-      </c>
+      <c r="G37" s="17">
+        <f t="shared" si="1"/>
+        <v>3.25</v>
+      </c>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -4354,20 +4286,18 @@
         <v>6</v>
       </c>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="14">
+      <c r="F38" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H38" s="17">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
+      <c r="G38" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -4378,22 +4308,22 @@
       <c r="C39" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D39" s="16"/>
+      <c r="D39" s="19"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="F39" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -4404,22 +4334,22 @@
       <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="16"/>
+      <c r="D40" s="19"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="F40" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -4430,22 +4360,22 @@
       <c r="C41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="16"/>
+      <c r="D41" s="19"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="F41" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -4460,20 +4390,20 @@
         <v>5.5</v>
       </c>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="14">
+      <c r="F42" s="14">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="H42" s="17">
-        <f t="shared" si="1"/>
-        <v>1.8333333333333333</v>
+      <c r="G42" s="17">
+        <f t="shared" si="1"/>
+        <v>2.75</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -4484,22 +4414,22 @@
       <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="16"/>
+      <c r="D43" s="19"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="F43" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G43" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -4510,30 +4440,1920 @@
       <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="16"/>
+      <c r="D44" s="19"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="17">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="F44" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G44" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:G2"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="I1:I3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75969961-D2E8-4C3C-997D-5ADAA35EF5FD}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="4">
+        <f>COUNT(A4:A44)</f>
+        <v>41</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25011001001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
+        <f>A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="20">
+        <v>25011001003</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A44" si="0">A5+1</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25011001004</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25011001005</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="21"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25011001006</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="21"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25011001007</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25011001008</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="21"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25011001009</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="21"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25011001011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="21"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25011001013</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25011001015</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="21"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25011001016</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25011001017</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25011001018</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25011001019</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25011001020</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25011001021</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="21"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25011001022</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="21"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25011001023</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="21"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25011001024</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="21"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25011001025</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25011001026</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="21"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25011001027</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="21"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25011001028</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="21"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25011001029</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="21"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25011001030</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="21"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25011001031</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25011001032</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="21"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>25011001033</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="20"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>25011001034</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="20"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="1">
+        <v>25011001036</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>25011001037</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="20"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="20">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="20">
+        <v>25011001038</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="20"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>25011001039</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="20"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="1">
+        <v>25011001040</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="20"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="1">
+        <v>24011001007</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="20"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>24011001026</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="20"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="1">
+        <v>24011001034</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="20"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="1">
+        <v>23011001003</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="20"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="1">
+        <v>23011001016</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="20"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="1">
+        <v>23011001023</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="20"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="22"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D46" s="22"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="22"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D48" s="22"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="22"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EBA74E-329D-4AC5-B37E-78AD71352384}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="26.33203125" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="30">
+        <v>7.5</v>
+      </c>
+      <c r="E1" s="30">
+        <v>7.5</v>
+      </c>
+      <c r="F1" s="30">
+        <v>15</v>
+      </c>
+      <c r="G1" s="31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="4">
+        <f>COUNT(A4:A44)</f>
+        <v>41</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="33"/>
+    </row>
+    <row r="3" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
+        <v>25011001001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="21">
+        <f>_xlfn.XLOOKUP(B4,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E4" s="21">
+        <f>_xlfn.XLOOKUP(B4,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F4" s="21">
+        <f>_xlfn.XLOOKUP(B4,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="23">
+        <f>CEILING(SUM(D4:F4),0.5)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
+        <f>A4+1</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="20">
+        <v>25011001003</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="21">
+        <f>_xlfn.XLOOKUP(B5,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E5" s="21">
+        <f>_xlfn.XLOOKUP(B5,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F5" s="21">
+        <f>_xlfn.XLOOKUP(B5,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="23">
+        <f t="shared" ref="G5:G44" si="0">CEILING(SUM(D5:F5),0.5)</f>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A44" si="1">A5+1</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>25011001004</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="21">
+        <f>_xlfn.XLOOKUP(B6,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="21">
+        <f>_xlfn.XLOOKUP(B6,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="21">
+        <f>_xlfn.XLOOKUP(B6,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="23">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>25011001005</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="21">
+        <f>_xlfn.XLOOKUP(B7,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="21">
+        <f>_xlfn.XLOOKUP(B7,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F7" s="21">
+        <f>_xlfn.XLOOKUP(B7,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="23">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>25011001006</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="21">
+        <f>_xlfn.XLOOKUP(B8,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="21">
+        <f>_xlfn.XLOOKUP(B8,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F8" s="21">
+        <f>_xlfn.XLOOKUP(B8,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25011001007</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="21">
+        <f>_xlfn.XLOOKUP(B9,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E9" s="21">
+        <f>_xlfn.XLOOKUP(B9,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F9" s="21">
+        <f>_xlfn.XLOOKUP(B9,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="23">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>25011001008</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="21">
+        <f>_xlfn.XLOOKUP(B10,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E10" s="21">
+        <f>_xlfn.XLOOKUP(B10,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F10" s="21">
+        <f>_xlfn.XLOOKUP(B10,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="23">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25011001009</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="21">
+        <f>_xlfn.XLOOKUP(B11,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E11" s="21">
+        <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F11" s="21">
+        <f>_xlfn.XLOOKUP(B11,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>25011001011</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="21">
+        <f>_xlfn.XLOOKUP(B12,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="21">
+        <f>_xlfn.XLOOKUP(B12,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="21">
+        <f>_xlfn.XLOOKUP(B12,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="23">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25011001013</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="21">
+        <f>_xlfn.XLOOKUP(B13,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="21">
+        <f>_xlfn.XLOOKUP(B13,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F13" s="21">
+        <f>_xlfn.XLOOKUP(B13,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>25011001015</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="21">
+        <f>_xlfn.XLOOKUP(B14,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>3</v>
+      </c>
+      <c r="E14" s="21">
+        <f>_xlfn.XLOOKUP(B14,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F14" s="21">
+        <f>_xlfn.XLOOKUP(B14,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="23">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>25011001016</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="21">
+        <f>_xlfn.XLOOKUP(B15,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E15" s="21">
+        <f>_xlfn.XLOOKUP(B15,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F15" s="21">
+        <f>_xlfn.XLOOKUP(B15,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="23">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>25011001017</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="21">
+        <f>_xlfn.XLOOKUP(B16,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E16" s="21">
+        <f>_xlfn.XLOOKUP(B16,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F16" s="21">
+        <f>_xlfn.XLOOKUP(B16,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>25011001018</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="21">
+        <f>_xlfn.XLOOKUP(B17,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="21">
+        <f>_xlfn.XLOOKUP(B17,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F17" s="21">
+        <f>_xlfn.XLOOKUP(B17,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>25011001019</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="21">
+        <f>_xlfn.XLOOKUP(B18,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E18" s="21">
+        <f>_xlfn.XLOOKUP(B18,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F18" s="21">
+        <f>_xlfn.XLOOKUP(B18,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="23">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>25011001020</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="21">
+        <f>_xlfn.XLOOKUP(B19,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E19" s="21">
+        <f>_xlfn.XLOOKUP(B19,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="21">
+        <f>_xlfn.XLOOKUP(B19,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="23">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25011001021</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="21">
+        <f>_xlfn.XLOOKUP(B20,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E20" s="21">
+        <f>_xlfn.XLOOKUP(B20,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F20" s="21">
+        <f>_xlfn.XLOOKUP(B20,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="23">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>25011001022</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="21">
+        <f>_xlfn.XLOOKUP(B21,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E21" s="21">
+        <f>_xlfn.XLOOKUP(B21,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F21" s="21">
+        <f>_xlfn.XLOOKUP(B21,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25011001023</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="21">
+        <f>_xlfn.XLOOKUP(B22,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="21">
+        <f>_xlfn.XLOOKUP(B22,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F22" s="21">
+        <f>_xlfn.XLOOKUP(B22,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>25011001024</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="21">
+        <f>_xlfn.XLOOKUP(B23,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E23" s="21">
+        <f>_xlfn.XLOOKUP(B23,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F23" s="21">
+        <f>_xlfn.XLOOKUP(B23,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="23">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25011001025</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="21">
+        <f>_xlfn.XLOOKUP(B24,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E24" s="21">
+        <f>_xlfn.XLOOKUP(B24,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F24" s="21">
+        <f>_xlfn.XLOOKUP(B24,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="23">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>25011001026</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="21">
+        <f>_xlfn.XLOOKUP(B25,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E25" s="21">
+        <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F25" s="21">
+        <f>_xlfn.XLOOKUP(B25,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="23">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25011001027</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="21">
+        <f>_xlfn.XLOOKUP(B26,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E26" s="21">
+        <f>_xlfn.XLOOKUP(B26,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F26" s="21">
+        <f>_xlfn.XLOOKUP(B26,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="23">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>25011001028</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="21">
+        <f>_xlfn.XLOOKUP(B27,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E27" s="21">
+        <f>_xlfn.XLOOKUP(B27,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F27" s="21">
+        <f>_xlfn.XLOOKUP(B27,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>25011001029</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="21">
+        <f>_xlfn.XLOOKUP(B28,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E28" s="21">
+        <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F28" s="21">
+        <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="23">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>25011001030</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="21">
+        <f>_xlfn.XLOOKUP(B29,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E29" s="21">
+        <f>_xlfn.XLOOKUP(B29,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F29" s="21">
+        <f>_xlfn.XLOOKUP(B29,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25011001031</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="21">
+        <f>_xlfn.XLOOKUP(B30,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E30" s="21">
+        <f>_xlfn.XLOOKUP(B30,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F30" s="21">
+        <f>_xlfn.XLOOKUP(B30,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="23">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>25011001032</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="21">
+        <f>_xlfn.XLOOKUP(B31,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>3</v>
+      </c>
+      <c r="E31" s="21">
+        <f>_xlfn.XLOOKUP(B31,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="F31" s="21">
+        <f>_xlfn.XLOOKUP(B31,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="23">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>25011001033</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="21">
+        <f>_xlfn.XLOOKUP(B32,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>3</v>
+      </c>
+      <c r="E32" s="21">
+        <f>_xlfn.XLOOKUP(B32,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F32" s="21">
+        <f>_xlfn.XLOOKUP(B32,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="23">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>25011001034</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="21">
+        <f>_xlfn.XLOOKUP(B33,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E33" s="21">
+        <f>_xlfn.XLOOKUP(B33,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F33" s="21">
+        <f>_xlfn.XLOOKUP(B33,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="1">
+        <v>25011001036</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="21">
+        <f>_xlfn.XLOOKUP(B34,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E34" s="21">
+        <f>_xlfn.XLOOKUP(B34,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F34" s="21">
+        <f>_xlfn.XLOOKUP(B34,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="1">
+        <v>25011001037</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="21">
+        <f>_xlfn.XLOOKUP(B35,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E35" s="21">
+        <f>_xlfn.XLOOKUP(B35,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F35" s="21">
+        <f>_xlfn.XLOOKUP(B35,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="23">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="20">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="20">
+        <v>25011001038</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="21">
+        <f>_xlfn.XLOOKUP(B36,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>6</v>
+      </c>
+      <c r="E36" s="21">
+        <f>_xlfn.XLOOKUP(B36,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F36" s="21">
+        <f>_xlfn.XLOOKUP(B36,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="23">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>25011001039</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="21">
+        <f>_xlfn.XLOOKUP(B37,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>7.5</v>
+      </c>
+      <c r="E37" s="21">
+        <f>_xlfn.XLOOKUP(B37,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3.25</v>
+      </c>
+      <c r="F37" s="21">
+        <f>_xlfn.XLOOKUP(B37,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="23">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="1">
+        <v>25011001040</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="21">
+        <f>_xlfn.XLOOKUP(B38,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E38" s="21">
+        <f>_xlfn.XLOOKUP(B38,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>3</v>
+      </c>
+      <c r="F38" s="21">
+        <f>_xlfn.XLOOKUP(B38,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="23">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="1">
+        <v>24011001007</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="21">
+        <f>_xlfn.XLOOKUP(B39,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="21">
+        <f>_xlfn.XLOOKUP(B39,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="21">
+        <f>_xlfn.XLOOKUP(B39,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>24011001026</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="21">
+        <f>_xlfn.XLOOKUP(B40,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="21">
+        <f>_xlfn.XLOOKUP(B40,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="21">
+        <f>_xlfn.XLOOKUP(B40,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="1">
+        <v>24011001034</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="21">
+        <f>_xlfn.XLOOKUP(B41,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="21">
+        <f>_xlfn.XLOOKUP(B41,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="21">
+        <f>_xlfn.XLOOKUP(B41,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="1">
+        <v>23011001003</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="21">
+        <f>_xlfn.XLOOKUP(B42,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="21">
+        <f>_xlfn.XLOOKUP(B42,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>2.75</v>
+      </c>
+      <c r="F42" s="21">
+        <f>_xlfn.XLOOKUP(B42,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="1">
+        <v>23011001016</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="21">
+        <f>_xlfn.XLOOKUP(B43,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="21">
+        <f>_xlfn.XLOOKUP(B43,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="21">
+        <f>_xlfn.XLOOKUP(B43,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="1">
+        <v>23011001023</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="21">
+        <f>_xlfn.XLOOKUP(B44,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
+        <v>3</v>
+      </c>
+      <c r="E44" s="21">
+        <f>_xlfn.XLOOKUP(B44,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="21">
+        <f>_xlfn.XLOOKUP(B44,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+    </row>
+    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{F1EBA74E-329D-4AC5-B37E-78AD71352384}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="G1:H2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="J1:J3"/>
-    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G4" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/ESE 2-1/Regular Assessment ESE 2-1.xlsx
+++ b/ESE 2-1/Regular Assessment ESE 2-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Assessment\ESE 2-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A33129-78C3-4CEF-9E57-B29E2E7530D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0038EE-0202-4BCC-A341-EEE995DBCF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESE 2-1 Attendance" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="73">
   <si>
     <t>SL</t>
   </si>
@@ -241,9 +241,6 @@
     <t>Comments on 2nd Assignemnt</t>
   </si>
   <si>
-    <t>Held, Tuck Loop</t>
-  </si>
-  <si>
     <t>Marks</t>
   </si>
   <si>
@@ -281,6 +278,12 @@
   </si>
   <si>
     <t>Class Test</t>
+  </si>
+  <si>
+    <t>Drew 3 Figures, Not Accurate &amp; Clear</t>
+  </si>
+  <si>
+    <t>Tuck, Miss Loop</t>
   </si>
 </sst>
 </file>
@@ -353,7 +356,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,6 +452,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD0CF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -515,7 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -584,6 +593,12 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -605,16 +620,13 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -992,15 +1004,17 @@
     <col min="10" max="10" width="30.77734375" style="2" customWidth="1"/>
     <col min="11" max="11" width="36.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="20" width="30.77734375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="30.77734375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="36.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="30.77734375" style="2" customWidth="1"/>
     <col min="21" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -1109,7 +1123,7 @@
         <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F3" s="9">
         <v>46257</v>
@@ -1135,7 +1149,9 @@
       <c r="M3" s="9">
         <v>46292</v>
       </c>
-      <c r="N3" s="9"/>
+      <c r="N3" s="9">
+        <v>46295</v>
+      </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="9"/>
@@ -1155,7 +1171,7 @@
       </c>
       <c r="D4" s="8">
         <f t="shared" ref="D4:D44" si="1">COUNTIF(F4:T4,"P")/(COUNTIF(F4:T4,"P")+COUNTIF(F4:T4,"A"))</f>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E4" s="1" cm="1">
         <f t="array" ref="E4">_xlfn.IFS(D4&gt;=90%,7.5,D4&gt;=80%,6,D4&gt;=70%,4.5,D4&gt;=60%,3,D4&lt;60%,0)</f>
@@ -1185,7 +1201,9 @@
       <c r="M4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1206,7 +1224,7 @@
       </c>
       <c r="D5" s="8">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E5" s="1" cm="1">
         <f t="array" ref="E5">_xlfn.IFS(D5&gt;=90%,7.5,D5&gt;=80%,6,D5&gt;=70%,4.5,D5&gt;=60%,3,D5&lt;60%,0)</f>
@@ -1236,7 +1254,9 @@
       <c r="M5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -1257,7 +1277,7 @@
       </c>
       <c r="D6" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E6" s="1" cm="1">
         <f t="array" ref="E6">_xlfn.IFS(D6&gt;=90%,7.5,D6&gt;=80%,6,D6&gt;=70%,4.5,D6&gt;=60%,3,D6&lt;60%,0)</f>
@@ -1287,7 +1307,9 @@
       <c r="M6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1338,7 +1360,9 @@
       <c r="M7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1389,7 +1413,9 @@
       <c r="M8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1410,7 +1436,7 @@
       </c>
       <c r="D9" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E9" s="1" cm="1">
         <f t="array" ref="E9">_xlfn.IFS(D9&gt;=90%,7.5,D9&gt;=80%,6,D9&gt;=70%,4.5,D9&gt;=60%,3,D9&lt;60%,0)</f>
@@ -1440,7 +1466,9 @@
       <c r="M9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1461,7 +1489,7 @@
       </c>
       <c r="D10" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.IFS(D10&gt;=90%,7.5,D10&gt;=80%,6,D10&gt;=70%,4.5,D10&gt;=60%,3,D10&lt;60%,0)</f>
@@ -1491,7 +1519,9 @@
       <c r="M10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1512,11 +1542,11 @@
       </c>
       <c r="D11" s="8">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E11" s="1" cm="1">
         <f t="array" ref="E11">_xlfn.IFS(D11&gt;=90%,7.5,D11&gt;=80%,6,D11&gt;=70%,4.5,D11&gt;=60%,3,D11&lt;60%,0)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>47</v>
@@ -1542,7 +1572,9 @@
       <c r="M11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="1"/>
+      <c r="N11" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
@@ -1563,7 +1595,7 @@
       </c>
       <c r="D12" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E12" s="1" cm="1">
         <f t="array" ref="E12">_xlfn.IFS(D12&gt;=90%,7.5,D12&gt;=80%,6,D12&gt;=70%,4.5,D12&gt;=60%,3,D12&lt;60%,0)</f>
@@ -1593,7 +1625,9 @@
       <c r="M12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
@@ -1644,7 +1678,9 @@
       <c r="M13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
@@ -1665,7 +1701,7 @@
       </c>
       <c r="D14" s="8">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E14" s="1" cm="1">
         <f t="array" ref="E14">_xlfn.IFS(D14&gt;=90%,7.5,D14&gt;=80%,6,D14&gt;=70%,4.5,D14&gt;=60%,3,D14&lt;60%,0)</f>
@@ -1695,7 +1731,9 @@
       <c r="M14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
@@ -1746,7 +1784,9 @@
       <c r="M15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
@@ -1797,7 +1837,9 @@
       <c r="M16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
@@ -1818,7 +1860,7 @@
       </c>
       <c r="D17" s="8">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E17" s="1" cm="1">
         <f t="array" ref="E17">_xlfn.IFS(D17&gt;=90%,7.5,D17&gt;=80%,6,D17&gt;=70%,4.5,D17&gt;=60%,3,D17&lt;60%,0)</f>
@@ -1848,7 +1890,9 @@
       <c r="M17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N17" s="1"/>
+      <c r="N17" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
@@ -1899,7 +1943,9 @@
       <c r="M18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -1920,7 +1966,7 @@
       </c>
       <c r="D19" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E19" s="1" cm="1">
         <f t="array" ref="E19">_xlfn.IFS(D19&gt;=90%,7.5,D19&gt;=80%,6,D19&gt;=70%,4.5,D19&gt;=60%,3,D19&lt;60%,0)</f>
@@ -1950,7 +1996,9 @@
       <c r="M19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
@@ -1971,7 +2019,7 @@
       </c>
       <c r="D20" s="8">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E20" s="1" cm="1">
         <f t="array" ref="E20">_xlfn.IFS(D20&gt;=90%,7.5,D20&gt;=80%,6,D20&gt;=70%,4.5,D20&gt;=60%,3,D20&lt;60%,0)</f>
@@ -2001,7 +2049,9 @@
       <c r="M20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -2052,7 +2102,9 @@
       <c r="M21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -2103,7 +2155,9 @@
       <c r="M22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -2124,7 +2178,7 @@
       </c>
       <c r="D23" s="8">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E23" s="1" cm="1">
         <f t="array" ref="E23">_xlfn.IFS(D23&gt;=90%,7.5,D23&gt;=80%,6,D23&gt;=70%,4.5,D23&gt;=60%,3,D23&lt;60%,0)</f>
@@ -2154,7 +2208,9 @@
       <c r="M23" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
@@ -2175,7 +2231,7 @@
       </c>
       <c r="D24" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E24" s="1" cm="1">
         <f t="array" ref="E24">_xlfn.IFS(D24&gt;=90%,7.5,D24&gt;=80%,6,D24&gt;=70%,4.5,D24&gt;=60%,3,D24&lt;60%,0)</f>
@@ -2205,7 +2261,9 @@
       <c r="M24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
@@ -2226,11 +2284,11 @@
       </c>
       <c r="D25" s="8">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E25" s="1" cm="1">
         <f t="array" ref="E25">_xlfn.IFS(D25&gt;=90%,7.5,D25&gt;=80%,6,D25&gt;=70%,4.5,D25&gt;=60%,3,D25&lt;60%,0)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>46</v>
@@ -2256,7 +2314,9 @@
       <c r="M25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N25" s="1"/>
+      <c r="N25" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
@@ -2277,7 +2337,7 @@
       </c>
       <c r="D26" s="8">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E26" s="1" cm="1">
         <f t="array" ref="E26">_xlfn.IFS(D26&gt;=90%,7.5,D26&gt;=80%,6,D26&gt;=70%,4.5,D26&gt;=60%,3,D26&lt;60%,0)</f>
@@ -2307,7 +2367,9 @@
       <c r="M26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2358,7 +2420,9 @@
       <c r="M27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -2379,11 +2443,11 @@
       </c>
       <c r="D28" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E28" s="1" cm="1">
         <f t="array" ref="E28">_xlfn.IFS(D28&gt;=90%,7.5,D28&gt;=80%,6,D28&gt;=70%,4.5,D28&gt;=60%,3,D28&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>47</v>
@@ -2409,7 +2473,9 @@
       <c r="M28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N28" s="1"/>
+      <c r="N28" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -2460,7 +2526,9 @@
       <c r="M29" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -2511,7 +2579,9 @@
       <c r="M30" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
@@ -2532,7 +2602,7 @@
       </c>
       <c r="D31" s="8">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E31" s="1" cm="1">
         <f t="array" ref="E31">_xlfn.IFS(D31&gt;=90%,7.5,D31&gt;=80%,6,D31&gt;=70%,4.5,D31&gt;=60%,3,D31&lt;60%,0)</f>
@@ -2562,7 +2632,9 @@
       <c r="M31" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N31" s="1"/>
+      <c r="N31" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -2583,7 +2655,7 @@
       </c>
       <c r="D32" s="8">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E32" s="1" cm="1">
         <f t="array" ref="E32">_xlfn.IFS(D32&gt;=90%,7.5,D32&gt;=80%,6,D32&gt;=70%,4.5,D32&gt;=60%,3,D32&lt;60%,0)</f>
@@ -2613,7 +2685,9 @@
       <c r="M32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -2664,7 +2738,9 @@
       <c r="M33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
@@ -2715,7 +2791,9 @@
       <c r="M34" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
@@ -2736,11 +2814,11 @@
       </c>
       <c r="D35" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E35" s="1" cm="1">
         <f t="array" ref="E35">_xlfn.IFS(D35&gt;=90%,7.5,D35&gt;=80%,6,D35&gt;=70%,4.5,D35&gt;=60%,3,D35&lt;60%,0)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>47</v>
@@ -2766,7 +2844,9 @@
       <c r="M35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N35" s="1"/>
+      <c r="N35" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -2787,7 +2867,7 @@
       </c>
       <c r="D36" s="8">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="E36" s="1" cm="1">
         <f t="array" ref="E36">_xlfn.IFS(D36&gt;=90%,7.5,D36&gt;=80%,6,D36&gt;=70%,4.5,D36&gt;=60%,3,D36&lt;60%,0)</f>
@@ -2817,7 +2897,9 @@
       <c r="M36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -2868,7 +2950,9 @@
       <c r="M37" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -2889,7 +2973,7 @@
       </c>
       <c r="D38" s="8">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E38" s="1" cm="1">
         <f t="array" ref="E38">_xlfn.IFS(D38&gt;=90%,7.5,D38&gt;=80%,6,D38&gt;=70%,4.5,D38&gt;=60%,3,D38&lt;60%,0)</f>
@@ -2919,7 +3003,9 @@
       <c r="M38" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -2940,7 +3026,7 @@
       </c>
       <c r="D39" s="8">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E39" s="1" cm="1">
         <f t="array" ref="E39">_xlfn.IFS(D39&gt;=90%,7.5,D39&gt;=80%,6,D39&gt;=70%,4.5,D39&gt;=60%,3,D39&lt;60%,0)</f>
@@ -2970,7 +3056,9 @@
       <c r="M39" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N39" s="1"/>
+      <c r="N39" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
@@ -2991,7 +3079,7 @@
       </c>
       <c r="D40" s="8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E40" s="1" cm="1">
         <f t="array" ref="E40">_xlfn.IFS(D40&gt;=90%,7.5,D40&gt;=80%,6,D40&gt;=70%,4.5,D40&gt;=60%,3,D40&lt;60%,0)</f>
@@ -3021,7 +3109,9 @@
       <c r="M40" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N40" s="1"/>
+      <c r="N40" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
@@ -3042,7 +3132,7 @@
       </c>
       <c r="D41" s="8">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="E41" s="1" cm="1">
         <f t="array" ref="E41">_xlfn.IFS(D41&gt;=90%,7.5,D41&gt;=80%,6,D41&gt;=70%,4.5,D41&gt;=60%,3,D41&lt;60%,0)</f>
@@ -3072,7 +3162,9 @@
       <c r="M41" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N41" s="1"/>
+      <c r="N41" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
@@ -3093,7 +3185,7 @@
       </c>
       <c r="D42" s="8">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E42" s="1" cm="1">
         <f t="array" ref="E42">_xlfn.IFS(D42&gt;=90%,7.5,D42&gt;=80%,6,D42&gt;=70%,4.5,D42&gt;=60%,3,D42&lt;60%,0)</f>
@@ -3123,7 +3215,9 @@
       <c r="M42" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N42" s="1"/>
+      <c r="N42" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
@@ -3144,7 +3238,7 @@
       </c>
       <c r="D43" s="8">
         <f t="shared" si="1"/>
-        <v>0.375</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="E43" s="1" cm="1">
         <f t="array" ref="E43">_xlfn.IFS(D43&gt;=90%,7.5,D43&gt;=80%,6,D43&gt;=70%,4.5,D43&gt;=60%,3,D43&lt;60%,0)</f>
@@ -3174,7 +3268,9 @@
       <c r="M43" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N43" s="1"/>
+      <c r="N43" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
@@ -3195,11 +3291,11 @@
       </c>
       <c r="D44" s="8">
         <f t="shared" si="1"/>
-        <v>0.625</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E44" s="1" cm="1">
         <f t="array" ref="E44">_xlfn.IFS(D44&gt;=90%,7.5,D44&gt;=80%,6,D44&gt;=70%,4.5,D44&gt;=60%,3,D44&lt;60%,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>47</v>
@@ -3225,7 +3321,9 @@
       <c r="M44" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N44" s="1"/>
+      <c r="N44" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
@@ -3288,16 +3386,16 @@
     <col min="5" max="5" width="21.44140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="8.6640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" customWidth="1"/>
-    <col min="8" max="8" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -3307,14 +3405,14 @@
       <c r="E1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26" t="s">
+      <c r="G1" s="27"/>
+      <c r="H1" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="29" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3327,18 +3425,18 @@
         <v>41</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="28"/>
+        <v>72</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="30"/>
     </row>
     <row r="3" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -3363,8 +3461,8 @@
       <c r="G3" s="13">
         <v>7.5</v>
       </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="29"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
@@ -3388,8 +3486,8 @@
         <f>F4/2</f>
         <v>2.75</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>63</v>
+      <c r="H4" s="25" t="s">
+        <v>62</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -3468,8 +3566,8 @@
         <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>60</v>
+      <c r="H7" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -3678,8 +3776,8 @@
         <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>60</v>
+      <c r="H15" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -3758,8 +3856,8 @@
         <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>61</v>
+      <c r="H18" s="25" t="s">
+        <v>60</v>
       </c>
       <c r="I18" s="1"/>
     </row>
@@ -3890,8 +3988,8 @@
         <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>60</v>
+      <c r="H23" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="I23" s="1"/>
     </row>
@@ -3944,8 +4042,8 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>64</v>
+      <c r="H25" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="I25" s="1"/>
     </row>
@@ -3972,8 +4070,8 @@
         <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>63</v>
+      <c r="H26" s="25" t="s">
+        <v>62</v>
       </c>
       <c r="I26" s="1"/>
     </row>
@@ -4015,19 +4113,19 @@
         <v>27</v>
       </c>
       <c r="D28" s="14">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G28" s="17">
         <f t="shared" si="1"/>
-        <v>2.25</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>60</v>
+        <v>2.5</v>
+      </c>
+      <c r="H28" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="I28" s="1"/>
     </row>
@@ -4106,8 +4204,8 @@
         <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>60</v>
+      <c r="H31" s="25" t="s">
+        <v>59</v>
       </c>
       <c r="I31" s="1"/>
     </row>
@@ -4134,8 +4232,8 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>64</v>
+      <c r="H32" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="I32" s="1"/>
     </row>
@@ -4214,8 +4312,8 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>64</v>
+      <c r="H35" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="I35" s="1"/>
     </row>
@@ -4318,8 +4416,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>62</v>
+      <c r="H39" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="I39" s="1"/>
     </row>
@@ -4334,17 +4432,19 @@
       <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="19"/>
+      <c r="D40" s="1">
+        <v>5.5</v>
+      </c>
       <c r="E40" s="1"/>
       <c r="F40" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="G40" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="1" t="s">
+        <v>2.75</v>
+      </c>
+      <c r="H40" s="25" t="s">
         <v>62</v>
       </c>
       <c r="I40" s="1"/>
@@ -4370,8 +4470,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>62</v>
+      <c r="H41" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="I41" s="1"/>
     </row>
@@ -4398,8 +4498,8 @@
         <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>63</v>
+      <c r="H42" s="25" t="s">
+        <v>62</v>
       </c>
       <c r="I42" s="1"/>
     </row>
@@ -4414,19 +4514,19 @@
       <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="19"/>
+      <c r="D43" s="1">
+        <v>6.5</v>
+      </c>
       <c r="E43" s="1"/>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="G43" s="17">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -4450,8 +4550,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>62</v>
+      <c r="H44" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="I44" s="1"/>
     </row>
@@ -4484,10 +4584,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
@@ -4502,10 +4602,10 @@
         <v>41</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -5087,7 +5187,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.21875" style="2" bestFit="1" customWidth="1"/>
@@ -5098,23 +5198,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="26"/>
       <c r="C1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="30">
+      <c r="D1" s="32">
         <v>7.5</v>
       </c>
-      <c r="E1" s="30">
+      <c r="E1" s="32">
         <v>7.5</v>
       </c>
-      <c r="F1" s="30">
+      <c r="F1" s="32">
         <v>15</v>
       </c>
-      <c r="G1" s="31">
+      <c r="G1" s="34">
         <v>30</v>
       </c>
     </row>
@@ -5127,12 +5227,12 @@
         <v>41</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="33"/>
+        <v>67</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -5145,13 +5245,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>71</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>53</v>
@@ -5365,7 +5465,7 @@
       </c>
       <c r="D11" s="21">
         <f>_xlfn.XLOOKUP(B11,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="21">
         <f>_xlfn.XLOOKUP(B11,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
@@ -5377,7 +5477,7 @@
       </c>
       <c r="G11" s="23">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -5757,7 +5857,7 @@
       </c>
       <c r="D25" s="21">
         <f>_xlfn.XLOOKUP(B25,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="E25" s="21">
         <f>_xlfn.XLOOKUP(B25,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
@@ -5769,7 +5869,7 @@
       </c>
       <c r="G25" s="23">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -5841,11 +5941,11 @@
       </c>
       <c r="D28" s="21">
         <f>_xlfn.XLOOKUP(B28,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="21">
         <f>_xlfn.XLOOKUP(B28,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="F28" s="21">
         <f>_xlfn.XLOOKUP(B28,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
@@ -5853,7 +5953,7 @@
       </c>
       <c r="G28" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -6037,7 +6137,7 @@
       </c>
       <c r="D35" s="21">
         <f>_xlfn.XLOOKUP(B35,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E35" s="21">
         <f>_xlfn.XLOOKUP(B35,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
@@ -6049,7 +6149,7 @@
       </c>
       <c r="G35" s="23">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -6181,7 +6281,7 @@
       </c>
       <c r="E40" s="21">
         <f>_xlfn.XLOOKUP(B40,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="F40" s="21">
         <f>_xlfn.XLOOKUP(B40,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
@@ -6189,7 +6289,7 @@
       </c>
       <c r="G40" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -6265,7 +6365,7 @@
       </c>
       <c r="E43" s="21">
         <f>_xlfn.XLOOKUP(B43,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="F43" s="21">
         <f>_xlfn.XLOOKUP(B43,'Class Test'!$B$4:$B$44,'Class Test'!$D$4:$D$44)</f>
@@ -6273,7 +6373,7 @@
       </c>
       <c r="G43" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6289,7 +6389,7 @@
       </c>
       <c r="D44" s="21">
         <f>_xlfn.XLOOKUP(B44,'ESE 2-1 Attendance'!$B$4:$B$44,'ESE 2-1 Attendance'!$E$4:$E$44)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" s="21">
         <f>_xlfn.XLOOKUP(B44,Assignment!$B$4:$B$44,Assignment!$G$4:$G$44)</f>
@@ -6301,44 +6401,8 @@
       </c>
       <c r="G44" s="23">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-    </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-    </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3" xr:uid="{F1EBA74E-329D-4AC5-B37E-78AD71352384}"/>
